--- a/NRM1_Cost_Estimate_Tool_v3_3.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v3_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\estates-ai-tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D28E4EB3-B773-461F-876B-632E2E99E9BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11311ED-0CE9-402C-BABF-489013970383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2465,13 +2465,13 @@
         <v>45</v>
       </c>
       <c r="E6" s="8">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F6" s="8">
         <v>40</v>
       </c>
       <c r="G6" s="8">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H6" s="8">
         <v>10</v>
@@ -2547,13 +2547,13 @@
         <v>45</v>
       </c>
       <c r="E8" s="8">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F8" s="8">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G8" s="8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H8" s="8">
         <v>10</v>
@@ -2696,16 +2696,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="8">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="I12" s="8">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J12" s="8">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K12" s="8">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="L12" s="8">
         <v>0</v>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="8">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I14" s="8">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="J14" s="8">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K14" s="8">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L14" s="8">
         <v>0</v>
@@ -3000,16 +3000,16 @@
         <v>110</v>
       </c>
       <c r="H20" s="8">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="I20" s="8">
-        <v>320</v>
+        <v>450</v>
       </c>
       <c r="J20" s="8">
-        <v>180</v>
+        <v>350</v>
       </c>
       <c r="K20" s="8">
-        <v>280</v>
+        <v>450</v>
       </c>
       <c r="L20" s="8">
         <v>0</v>
@@ -3032,25 +3032,25 @@
         <v>59</v>
       </c>
       <c r="E21" s="8">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F21" s="8">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="G21" s="8">
         <v>200</v>
       </c>
       <c r="H21" s="8">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="I21" s="8">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="J21" s="8">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="K21" s="8">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L21" s="8">
         <v>0</v>
@@ -3111,28 +3111,28 @@
         <v>93</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="E23" s="8">
         <v>15</v>
       </c>
       <c r="F23" s="8">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G23" s="8">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H23" s="8">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I23" s="8">
+        <v>60</v>
+      </c>
+      <c r="J23" s="8">
         <v>35</v>
       </c>
-      <c r="J23" s="8">
-        <v>18</v>
-      </c>
       <c r="K23" s="8">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="L23" s="8">
         <v>0</v>
@@ -3254,7 +3254,7 @@
         <v>59</v>
       </c>
       <c r="E27" s="8">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F27" s="8">
         <v>75</v>
@@ -3397,22 +3397,22 @@
         <v>900</v>
       </c>
       <c r="F31" s="8">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="G31" s="8">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="H31" s="8">
-        <v>900</v>
+        <v>2000</v>
       </c>
       <c r="I31" s="8">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="J31" s="8">
-        <v>8</v>
+        <v>2000</v>
       </c>
       <c r="K31" s="8">
-        <v>18</v>
+        <v>3500</v>
       </c>
       <c r="L31" s="8">
         <v>0</v>
@@ -3435,25 +3435,25 @@
         <v>94</v>
       </c>
       <c r="E32" s="8">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="F32" s="8">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="G32" s="8">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="H32" s="8">
-        <v>2500</v>
+        <v>6000</v>
       </c>
       <c r="I32" s="8">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="J32" s="8">
-        <v>5</v>
+        <v>6000</v>
       </c>
       <c r="K32" s="8">
-        <v>15</v>
+        <v>10000</v>
       </c>
       <c r="L32" s="8">
         <v>0</v>
@@ -3479,22 +3479,22 @@
         <v>0</v>
       </c>
       <c r="F33" s="8">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G33" s="8">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="H33" s="8">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="I33" s="8">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="J33" s="8">
         <v>0</v>
       </c>
       <c r="K33" s="8">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="L33" s="8">
         <v>0</v>
@@ -4511,25 +4511,25 @@
         <v>94</v>
       </c>
       <c r="E60" s="8">
-        <v>50</v>
+        <v>25000</v>
       </c>
       <c r="F60" s="8">
-        <v>80</v>
+        <v>40000</v>
       </c>
       <c r="G60" s="8">
-        <v>120</v>
+        <v>60000</v>
       </c>
       <c r="H60" s="8">
-        <v>60</v>
+        <v>40000</v>
       </c>
       <c r="I60" s="8">
-        <v>100</v>
+        <v>60000</v>
       </c>
       <c r="J60" s="8">
-        <v>50</v>
+        <v>40000</v>
       </c>
       <c r="K60" s="8">
-        <v>90</v>
+        <v>60000</v>
       </c>
       <c r="L60" s="8">
         <v>0</v>

--- a/NRM1_Cost_Estimate_Tool_v3_3.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v3_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\estates-ai-tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11311ED-0CE9-402C-BABF-489013970383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F7AA89E-2DCB-4704-B5B0-682D65BF53FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1806,7 +1806,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1921,6 +1921,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2462,7 +2465,7 @@
         <v>44</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E6" s="8">
         <v>25</v>
@@ -2503,7 +2506,7 @@
         <v>48</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E7" s="8">
         <v>20</v>
@@ -2544,7 +2547,7 @@
         <v>51</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E8" s="8">
         <v>15</v>
@@ -2585,7 +2588,7 @@
         <v>54</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E9" s="8">
         <v>5</v>
@@ -2766,7 +2769,7 @@
         <v>68</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E14" s="8">
         <v>0</v>
@@ -2947,7 +2950,7 @@
         <v>81</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E19" s="8">
         <v>10</v>
@@ -3350,7 +3353,7 @@
         <v>111</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E30" s="8">
         <v>10</v>
@@ -3476,25 +3479,25 @@
         <v>45</v>
       </c>
       <c r="E33" s="8">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="F33" s="8">
-        <v>100</v>
+        <v>7500</v>
       </c>
       <c r="G33" s="8">
-        <v>200</v>
+        <v>10000</v>
       </c>
       <c r="H33" s="8">
-        <v>100</v>
+        <v>7500</v>
       </c>
       <c r="I33" s="8">
-        <v>200</v>
+        <v>10000</v>
       </c>
       <c r="J33" s="8">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="K33" s="8">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="L33" s="8">
         <v>0</v>
@@ -3514,13 +3517,13 @@
         <v>123</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E34" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F34" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G34" s="8">
         <v>15</v>
@@ -3657,7 +3660,7 @@
         <v>45</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="F38">
         <v>3500</v>
@@ -3777,7 +3780,7 @@
         <v>142</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E41" s="8">
         <v>5</v>
@@ -4186,17 +4189,17 @@
       <c r="C51" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D51" s="8" t="s">
-        <v>45</v>
+      <c r="D51" t="s">
+        <v>59</v>
       </c>
       <c r="E51" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F51" s="8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G51" s="8">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H51" s="8">
         <v>5</v>
@@ -4231,7 +4234,7 @@
         <v>176</v>
       </c>
       <c r="E52" s="8">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F52" s="8">
         <v>800</v>
@@ -4272,7 +4275,7 @@
         <v>180</v>
       </c>
       <c r="E53" s="8">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F53" s="8">
         <v>400</v>
@@ -4310,10 +4313,10 @@
         <v>183</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E54" s="8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F54" s="8">
         <v>30</v>
@@ -4354,7 +4357,7 @@
         <v>59</v>
       </c>
       <c r="E55" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F55" s="8">
         <v>8</v>
@@ -4450,19 +4453,19 @@
         <v>192</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E58" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F58" s="8">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G58" s="8">
         <v>50</v>
       </c>
       <c r="H58" s="8">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I58" s="8">
         <v>40</v>
@@ -4580,9 +4583,21 @@
       </c>
     </row>
     <row r="62" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="53" t="s">
         <v>200</v>
       </c>
+      <c r="B62" s="53"/>
+      <c r="C62" s="53"/>
+      <c r="D62" s="53"/>
+      <c r="E62" s="53"/>
+      <c r="F62" s="53"/>
+      <c r="G62" s="53"/>
+      <c r="H62" s="53"/>
+      <c r="I62" s="53"/>
+      <c r="J62" s="53"/>
+      <c r="K62" s="53"/>
+      <c r="L62" s="53"/>
+      <c r="M62" s="53"/>
     </row>
     <row r="63" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="8">
@@ -4636,10 +4651,10 @@
         <v>205</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E64" s="8">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F64" s="8">
         <v>50</v>
@@ -4694,7 +4709,7 @@
         <v>209</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E66" s="8">
         <v>10</v>
@@ -4735,7 +4750,7 @@
         <v>212</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E67" s="8">
         <v>10</v>
@@ -4776,7 +4791,7 @@
         <v>215</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E68" s="8">
         <v>5</v>
@@ -4817,7 +4832,7 @@
         <v>218</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E69" s="8">
         <v>0</v>
@@ -4858,7 +4873,7 @@
         <v>221</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E70" s="8">
         <v>5</v>
@@ -4904,7 +4919,7 @@
         <v>225</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E72" s="8">
         <v>3</v>
@@ -4989,10 +5004,10 @@
         <v>94</v>
       </c>
       <c r="E74" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F74" s="8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G74" s="8">
         <v>10</v>
@@ -5085,16 +5100,16 @@
         <v>237</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E77" s="8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F77" s="8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G77" s="8">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H77" s="8">
         <v>10</v>
@@ -5129,28 +5144,28 @@
         <v>59</v>
       </c>
       <c r="E78" s="8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F78" s="8">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="G78" s="8">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="H78" s="8">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="I78" s="8">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="J78" s="8">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="K78" s="8">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="L78" s="8">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="M78" s="9" t="s">
         <v>241</v>
@@ -5167,7 +5182,7 @@
         <v>243</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E79" s="8">
         <v>0</v>
@@ -5208,28 +5223,28 @@
         <v>246</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="E80" s="8">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F80" s="8">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="G80" s="8">
-        <v>5</v>
+        <v>250</v>
       </c>
       <c r="H80" s="8">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="I80" s="8">
-        <v>8</v>
+        <v>250</v>
       </c>
       <c r="J80" s="8">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="K80" s="8">
-        <v>6</v>
+        <v>250</v>
       </c>
       <c r="L80" s="8">
         <v>10</v>
@@ -5244,7 +5259,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="A76:M76"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A5:M5"/>
@@ -5257,6 +5272,7 @@
     <mergeCell ref="A59:M59"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A62:M62"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/NRM1_Cost_Estimate_Tool_v3_3.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v3_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\estates-ai-tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F7AA89E-2DCB-4704-B5B0-682D65BF53FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6760775B-5EB1-4548-8004-43C0FB256935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1916,14 +1916,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4583,21 +4583,21 @@
       </c>
     </row>
     <row r="62" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="53" t="s">
+      <c r="A62" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="B62" s="53"/>
-      <c r="C62" s="53"/>
-      <c r="D62" s="53"/>
-      <c r="E62" s="53"/>
-      <c r="F62" s="53"/>
-      <c r="G62" s="53"/>
-      <c r="H62" s="53"/>
-      <c r="I62" s="53"/>
-      <c r="J62" s="53"/>
-      <c r="K62" s="53"/>
-      <c r="L62" s="53"/>
-      <c r="M62" s="53"/>
+      <c r="B62" s="51"/>
+      <c r="C62" s="51"/>
+      <c r="D62" s="51"/>
+      <c r="E62" s="51"/>
+      <c r="F62" s="51"/>
+      <c r="G62" s="51"/>
+      <c r="H62" s="51"/>
+      <c r="I62" s="51"/>
+      <c r="J62" s="51"/>
+      <c r="K62" s="51"/>
+      <c r="L62" s="51"/>
+      <c r="M62" s="51"/>
     </row>
     <row r="63" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="8">
@@ -4610,7 +4610,7 @@
         <v>202</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E63" s="8">
         <v>0</v>
@@ -5042,7 +5042,7 @@
         <v>234</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E75" s="8">
         <v>3</v>
@@ -6563,13 +6563,13 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="51"/>
+      <c r="A14" s="52"/>
       <c r="B14" s="48"/>
       <c r="C14" s="48"/>
       <c r="D14" s="48"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="52" t="s">
+      <c r="A15" s="53" t="s">
         <v>398</v>
       </c>
       <c r="B15" s="48"/>

--- a/NRM1_Cost_Estimate_Tool_v3_3.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v3_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\estates-ai-tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6760775B-5EB1-4548-8004-43C0FB256935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9EB4DA-432A-40CF-B30E-5FE15BBD6E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="532">
   <si>
     <t>NRM1 COST ESTIMATE TOOL — v3.0</t>
   </si>
@@ -772,9 +772,6 @@
     <t>Column/wall lighting (see also 5.10)</t>
   </si>
   <si>
-    <t>UPDATE LOG: v3.0 May 2026 — Rebuilt. v3.1 May 2026 — Rate calibration: 5.1→65, 5.8→70, 5.9→32(split), 5.7→38, 5.20→18. 4.2 sanitary per-Nr (900 Std), 4.3 kitchen per-Nr (3500 Std). 0.1→40, 2.7→50. v3.2 May 2026 — Granular M&amp;E added per Q v6: 5.2L(3500/Item), 5.7a(18/m²), 5.8a(22/m²), 5.8b(15/m²), 5.8c(18/m²), 5.9a(18/m²), 5.9b(10/m²). 5.9 split into 5.9a+5.9b. Tab5 Q2.3 options renamed: Like-for-like added; Full refurbishment→Refurbishment; Complete strip-out→Strip-out and rebuild. Coordinated with Questionnaire v6.0. All rates BCIS Q1 2026/C&amp;W 2025/RICS 2025. Next review Q4 2026.</t>
-  </si>
-  <si>
     <t>PERCENTAGE RULES — all additions A–H | machine-readable | EDIT RULES HERE</t>
   </si>
   <si>
@@ -1607,6 +1604,24 @@
   </si>
   <si>
     <t>Separated from 5.9a fire alarm.</t>
+  </si>
+  <si>
+    <t>Per 7kW point inc groundworks</t>
+  </si>
+  <si>
+    <t>Access control &amp; CCTV / security</t>
+  </si>
+  <si>
+    <t>Door access, CCTV; varies by level</t>
+  </si>
+  <si>
+    <t>8.5</t>
+  </si>
+  <si>
+    <t>Foul drainage connections</t>
+  </si>
+  <si>
+    <t>Connection to existing or new manhole</t>
   </si>
 </sst>
 </file>
@@ -1755,7 +1770,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1789,24 +1804,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1814,14 +1816,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1905,9 +1901,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1923,6 +1916,19 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2363,1286 +2369,1286 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
     </row>
     <row r="2" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="5" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="48"/>
-      <c r="M5" s="48"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
-        <v>0</v>
-      </c>
-      <c r="B6" s="8" t="s">
+      <c r="A6" s="6">
+        <v>0</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="6">
         <v>25</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="6">
         <v>40</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="6">
         <v>90</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="6">
         <v>10</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="6">
         <v>20</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="6">
         <v>10</v>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="6">
         <v>20</v>
       </c>
-      <c r="L6" s="8">
-        <v>0</v>
-      </c>
-      <c r="M6" s="9" t="s">
+      <c r="L6" s="6">
+        <v>0</v>
+      </c>
+      <c r="M6" s="7" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
-        <v>0</v>
-      </c>
-      <c r="B7" s="8" t="s">
+      <c r="A7" s="6">
+        <v>0</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="6">
         <v>20</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="6">
         <v>35</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="6">
         <v>55</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="6">
         <v>15</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="6">
         <v>25</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="6">
         <v>20</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K7" s="6">
         <v>35</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="6">
         <v>5</v>
       </c>
-      <c r="M7" s="9" t="s">
+      <c r="M7" s="7" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
-        <v>0</v>
-      </c>
-      <c r="B8" s="8" t="s">
+      <c r="A8" s="6">
+        <v>0</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="6">
         <v>15</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="6">
         <v>30</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="6">
         <v>40</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="6">
         <v>10</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="6">
         <v>20</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="6">
         <v>5</v>
       </c>
-      <c r="K8" s="8">
+      <c r="K8" s="6">
         <v>15</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="6">
         <v>10</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="M8" s="7" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
-        <v>0</v>
-      </c>
-      <c r="B9" s="8" t="s">
+      <c r="A9" s="6">
+        <v>0</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="6">
         <v>5</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="6">
         <v>8</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="6">
         <v>15</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="6">
         <v>8</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="6">
         <v>15</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="6">
         <v>5</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="6">
         <v>12</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="6">
         <v>5</v>
       </c>
-      <c r="M9" s="9" t="s">
+      <c r="M9" s="7" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="48"/>
-      <c r="M10" s="48"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+      <c r="A11" s="6">
         <v>1</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E11" s="8">
-        <v>0</v>
-      </c>
-      <c r="F11" s="8">
-        <v>0</v>
-      </c>
-      <c r="G11" s="8">
-        <v>0</v>
-      </c>
-      <c r="H11" s="8">
+      <c r="E11" s="6">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6">
         <v>55</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="6">
         <v>80</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="6">
         <v>55</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="6">
         <v>80</v>
       </c>
-      <c r="L11" s="8">
-        <v>0</v>
-      </c>
-      <c r="M11" s="9" t="s">
+      <c r="L11" s="6">
+        <v>0</v>
+      </c>
+      <c r="M11" s="7" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+      <c r="A12" s="6">
         <v>1</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="8">
-        <v>0</v>
-      </c>
-      <c r="F12" s="8">
-        <v>0</v>
-      </c>
-      <c r="G12" s="8">
-        <v>0</v>
-      </c>
-      <c r="H12" s="8">
+      <c r="E12" s="6">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6">
         <v>55</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="6">
         <v>90</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="6">
         <v>55</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12" s="6">
         <v>90</v>
       </c>
-      <c r="L12" s="8">
-        <v>0</v>
-      </c>
-      <c r="M12" s="9" t="s">
+      <c r="L12" s="6">
+        <v>0</v>
+      </c>
+      <c r="M12" s="7" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+      <c r="A13" s="6">
         <v>1</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="8">
-        <v>0</v>
-      </c>
-      <c r="F13" s="8">
-        <v>0</v>
-      </c>
-      <c r="G13" s="8">
-        <v>0</v>
-      </c>
-      <c r="H13" s="8">
+      <c r="E13" s="6">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6">
         <v>35</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="6">
         <v>55</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="6">
         <v>35</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13" s="6">
         <v>55</v>
       </c>
-      <c r="L13" s="8">
-        <v>0</v>
-      </c>
-      <c r="M13" s="9" t="s">
+      <c r="L13" s="6">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+      <c r="A14" s="6">
         <v>1</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="8">
-        <v>0</v>
-      </c>
-      <c r="F14" s="8">
-        <v>0</v>
-      </c>
-      <c r="G14" s="8">
-        <v>0</v>
-      </c>
-      <c r="H14" s="8">
+      <c r="E14" s="6">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6">
         <v>100</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="6">
         <v>200</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="6">
         <v>100</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="6">
         <v>200</v>
       </c>
-      <c r="L14" s="8">
-        <v>0</v>
-      </c>
-      <c r="M14" s="9" t="s">
+      <c r="L14" s="6">
+        <v>0</v>
+      </c>
+      <c r="M14" s="7" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="49" t="s">
+      <c r="A15" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="48"/>
-      <c r="L15" s="48"/>
-      <c r="M15" s="48"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="43"/>
+      <c r="M15" s="43"/>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+      <c r="A16" s="6">
         <v>2</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="8">
-        <v>0</v>
-      </c>
-      <c r="F16" s="8">
+      <c r="E16" s="6">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6">
         <v>20</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="6">
         <v>40</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="6">
         <v>150</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="6">
         <v>220</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="6">
         <v>130</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K16" s="6">
         <v>200</v>
       </c>
-      <c r="L16" s="8">
-        <v>0</v>
-      </c>
-      <c r="M16" s="9" t="s">
+      <c r="L16" s="6">
+        <v>0</v>
+      </c>
+      <c r="M16" s="7" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+      <c r="A17" s="6">
         <v>2</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E17" s="8">
-        <v>0</v>
-      </c>
-      <c r="F17" s="8">
+      <c r="E17" s="6">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6">
         <v>15</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="6">
         <v>30</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="6">
         <v>65</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="6">
         <v>95</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="6">
         <v>65</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K17" s="6">
         <v>95</v>
       </c>
-      <c r="L17" s="8">
-        <v>0</v>
-      </c>
-      <c r="M17" s="9" t="s">
+      <c r="L17" s="6">
+        <v>0</v>
+      </c>
+      <c r="M17" s="7" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
+      <c r="A18" s="6">
         <v>2</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="6">
         <v>35</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="6">
         <v>55</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="6">
         <v>90</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="6">
         <v>75</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="6">
         <v>120</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="6">
         <v>75</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="6">
         <v>120</v>
       </c>
-      <c r="L18" s="8">
-        <v>0</v>
-      </c>
-      <c r="M18" s="9" t="s">
+      <c r="L18" s="6">
+        <v>0</v>
+      </c>
+      <c r="M18" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+      <c r="A19" s="6">
         <v>2</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="6">
         <v>10</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="6">
         <v>15</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="6">
         <v>25</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="6">
         <v>20</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="6">
         <v>35</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="6">
         <v>20</v>
       </c>
-      <c r="K19" s="8">
+      <c r="K19" s="6">
         <v>35</v>
       </c>
-      <c r="L19" s="8">
-        <v>0</v>
-      </c>
-      <c r="M19" s="9" t="s">
+      <c r="L19" s="6">
+        <v>0</v>
+      </c>
+      <c r="M19" s="7" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
+      <c r="A20" s="6">
         <v>2</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="6">
         <v>30</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="6">
         <v>60</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="6">
         <v>110</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="6">
         <v>350</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="6">
         <v>450</v>
       </c>
-      <c r="J20" s="8">
+      <c r="J20" s="6">
         <v>350</v>
       </c>
-      <c r="K20" s="8">
+      <c r="K20" s="6">
         <v>450</v>
       </c>
-      <c r="L20" s="8">
-        <v>0</v>
-      </c>
-      <c r="M20" s="9" t="s">
+      <c r="L20" s="6">
+        <v>0</v>
+      </c>
+      <c r="M20" s="7" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+      <c r="A21" s="6">
         <v>2</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="6">
         <v>100</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="6">
         <v>150</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="6">
         <v>200</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="6">
         <v>180</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="6">
         <v>240</v>
       </c>
-      <c r="J21" s="8">
+      <c r="J21" s="6">
         <v>150</v>
       </c>
-      <c r="K21" s="8">
+      <c r="K21" s="6">
         <v>200</v>
       </c>
-      <c r="L21" s="8">
-        <v>0</v>
-      </c>
-      <c r="M21" s="9" t="s">
+      <c r="L21" s="6">
+        <v>0</v>
+      </c>
+      <c r="M21" s="7" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+      <c r="A22" s="6">
         <v>2</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="6">
         <v>20</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="6">
         <v>50</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="6">
         <v>75</v>
       </c>
-      <c r="H22" s="8">
+      <c r="H22" s="6">
         <v>30</v>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="6">
         <v>50</v>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="6">
         <v>25</v>
       </c>
-      <c r="K22" s="8">
+      <c r="K22" s="6">
         <v>45</v>
       </c>
-      <c r="L22" s="8">
-        <v>0</v>
-      </c>
-      <c r="M22" s="9" t="s">
+      <c r="L22" s="6">
+        <v>0</v>
+      </c>
+      <c r="M22" s="7" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
+      <c r="A23" s="6">
         <v>2</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="6">
         <v>15</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="6">
         <v>35</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="6">
         <v>60</v>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="6">
         <v>35</v>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="6">
         <v>60</v>
       </c>
-      <c r="J23" s="8">
+      <c r="J23" s="6">
         <v>35</v>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="6">
         <v>60</v>
       </c>
-      <c r="L23" s="8">
-        <v>0</v>
-      </c>
-      <c r="M23" s="9" t="s">
+      <c r="L23" s="6">
+        <v>0</v>
+      </c>
+      <c r="M23" s="7" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
+      <c r="A24" s="6">
         <v>2</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="6">
         <v>12</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="6">
         <v>22</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="6">
         <v>40</v>
       </c>
-      <c r="H24" s="8">
+      <c r="H24" s="6">
         <v>15</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="6">
         <v>28</v>
       </c>
-      <c r="J24" s="8">
+      <c r="J24" s="6">
         <v>12</v>
       </c>
-      <c r="K24" s="8">
+      <c r="K24" s="6">
         <v>24</v>
       </c>
-      <c r="L24" s="8">
-        <v>0</v>
-      </c>
-      <c r="M24" s="10" t="s">
+      <c r="L24" s="6">
+        <v>0</v>
+      </c>
+      <c r="M24" s="8" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="B25" s="48"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="48"/>
-      <c r="K25" s="48"/>
-      <c r="L25" s="48"/>
-      <c r="M25" s="48"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="43"/>
+      <c r="M25" s="43"/>
     </row>
     <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8">
+      <c r="A26" s="6">
         <v>3</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="6">
         <v>30</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="6">
         <v>55</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="6">
         <v>75</v>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="6">
         <v>25</v>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="6">
         <v>55</v>
       </c>
-      <c r="J26" s="8">
+      <c r="J26" s="6">
         <v>20</v>
       </c>
-      <c r="K26" s="8">
+      <c r="K26" s="6">
         <v>50</v>
       </c>
-      <c r="L26" s="8">
-        <v>0</v>
-      </c>
-      <c r="M26" s="9" t="s">
+      <c r="L26" s="6">
+        <v>0</v>
+      </c>
+      <c r="M26" s="7" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="8">
+      <c r="A27" s="6">
         <v>3</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="6">
         <v>35</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="6">
         <v>75</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="6">
         <v>130</v>
       </c>
-      <c r="H27" s="8">
+      <c r="H27" s="6">
         <v>30</v>
       </c>
-      <c r="I27" s="8">
+      <c r="I27" s="6">
         <v>80</v>
       </c>
-      <c r="J27" s="8">
+      <c r="J27" s="6">
         <v>25</v>
       </c>
-      <c r="K27" s="8">
+      <c r="K27" s="6">
         <v>70</v>
       </c>
-      <c r="L27" s="8">
-        <v>0</v>
-      </c>
-      <c r="M27" s="9" t="s">
+      <c r="L27" s="6">
+        <v>0</v>
+      </c>
+      <c r="M27" s="7" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="8">
+      <c r="A28" s="6">
         <v>3</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="6">
         <v>30</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="6">
         <v>45</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="6">
         <v>85</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="6">
         <v>15</v>
       </c>
-      <c r="I28" s="8">
+      <c r="I28" s="6">
         <v>45</v>
       </c>
-      <c r="J28" s="8">
+      <c r="J28" s="6">
         <v>12</v>
       </c>
-      <c r="K28" s="8">
+      <c r="K28" s="6">
         <v>40</v>
       </c>
-      <c r="L28" s="8">
-        <v>0</v>
-      </c>
-      <c r="M28" s="9" t="s">
+      <c r="L28" s="6">
+        <v>0</v>
+      </c>
+      <c r="M28" s="7" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="49" t="s">
+      <c r="A29" s="44" t="s">
         <v>109</v>
       </c>
-      <c r="B29" s="48"/>
-      <c r="C29" s="48"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="48"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="48"/>
-      <c r="K29" s="48"/>
-      <c r="L29" s="48"/>
-      <c r="M29" s="48"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="43"/>
+      <c r="L29" s="43"/>
+      <c r="M29" s="43"/>
     </row>
     <row r="30" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="8">
+      <c r="A30" s="6">
         <v>4</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="6">
         <v>10</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="6">
         <v>45</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="6">
         <v>100</v>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="6">
         <v>15</v>
       </c>
-      <c r="I30" s="8">
+      <c r="I30" s="6">
         <v>50</v>
       </c>
-      <c r="J30" s="8">
+      <c r="J30" s="6">
         <v>10</v>
       </c>
-      <c r="K30" s="8">
+      <c r="K30" s="6">
         <v>40</v>
       </c>
-      <c r="L30" s="8">
-        <v>0</v>
-      </c>
-      <c r="M30" s="9" t="s">
+      <c r="L30" s="6">
+        <v>0</v>
+      </c>
+      <c r="M30" s="7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="8">
+      <c r="A31" s="6">
         <v>4</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="6">
         <v>900</v>
       </c>
-      <c r="F31" s="8">
+      <c r="F31" s="6">
         <v>2000</v>
       </c>
-      <c r="G31" s="8">
+      <c r="G31" s="6">
         <v>3500</v>
       </c>
-      <c r="H31" s="8">
+      <c r="H31" s="6">
         <v>2000</v>
       </c>
-      <c r="I31" s="8">
+      <c r="I31" s="6">
         <v>3500</v>
       </c>
-      <c r="J31" s="8">
+      <c r="J31" s="6">
         <v>2000</v>
       </c>
-      <c r="K31" s="8">
+      <c r="K31" s="6">
         <v>3500</v>
       </c>
-      <c r="L31" s="8">
-        <v>0</v>
-      </c>
-      <c r="M31" s="9" t="s">
+      <c r="L31" s="6">
+        <v>0</v>
+      </c>
+      <c r="M31" s="7" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="8">
+      <c r="A32" s="6">
         <v>4</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="6">
         <v>3500</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F32" s="6">
         <v>6000</v>
       </c>
-      <c r="G32" s="8">
+      <c r="G32" s="6">
         <v>10000</v>
       </c>
-      <c r="H32" s="8">
+      <c r="H32" s="6">
         <v>6000</v>
       </c>
-      <c r="I32" s="8">
+      <c r="I32" s="6">
         <v>10000</v>
       </c>
-      <c r="J32" s="8">
+      <c r="J32" s="6">
         <v>6000</v>
       </c>
-      <c r="K32" s="8">
+      <c r="K32" s="6">
         <v>10000</v>
       </c>
-      <c r="L32" s="8">
-        <v>0</v>
-      </c>
-      <c r="M32" s="9" t="s">
+      <c r="L32" s="6">
+        <v>0</v>
+      </c>
+      <c r="M32" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="8">
+      <c r="A33" s="6">
         <v>4</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="6">
         <v>5000</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="6">
         <v>7500</v>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="6">
         <v>10000</v>
       </c>
-      <c r="H33" s="8">
+      <c r="H33" s="6">
         <v>7500</v>
       </c>
-      <c r="I33" s="8">
+      <c r="I33" s="6">
         <v>10000</v>
       </c>
-      <c r="J33" s="8">
+      <c r="J33" s="6">
         <v>7500</v>
       </c>
-      <c r="K33" s="8">
+      <c r="K33" s="6">
         <v>10000</v>
       </c>
-      <c r="L33" s="8">
-        <v>0</v>
-      </c>
-      <c r="M33" s="9" t="s">
+      <c r="L33" s="6">
+        <v>0</v>
+      </c>
+      <c r="M33" s="7" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="8">
+      <c r="A34" s="6">
         <v>4</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E34" s="8">
+      <c r="E34" s="6">
         <v>5</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F34" s="6">
         <v>10</v>
       </c>
-      <c r="G34" s="8">
+      <c r="G34" s="6">
         <v>15</v>
       </c>
-      <c r="H34" s="8">
+      <c r="H34" s="6">
         <v>3</v>
       </c>
-      <c r="I34" s="8">
+      <c r="I34" s="6">
         <v>10</v>
       </c>
-      <c r="J34" s="8">
+      <c r="J34" s="6">
         <v>2</v>
       </c>
-      <c r="K34" s="8">
+      <c r="K34" s="6">
         <v>8</v>
       </c>
-      <c r="L34" s="8">
+      <c r="L34" s="6">
         <v>5</v>
       </c>
-      <c r="M34" s="10" t="s">
+      <c r="M34" s="8" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="49" t="s">
+      <c r="A35" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="B35" s="48"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48"/>
-      <c r="J35" s="48"/>
-      <c r="K35" s="48"/>
-      <c r="L35" s="48"/>
-      <c r="M35" s="48"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="43"/>
+      <c r="L35" s="43"/>
+      <c r="M35" s="43"/>
     </row>
     <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="8">
+      <c r="A36" s="6">
         <v>5</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E36" s="8">
+      <c r="E36" s="6">
         <v>30</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F36" s="6">
         <v>65</v>
       </c>
-      <c r="G36" s="8">
+      <c r="G36" s="6">
         <v>110</v>
       </c>
-      <c r="H36" s="8">
+      <c r="H36" s="6">
         <v>25</v>
       </c>
-      <c r="I36" s="8">
+      <c r="I36" s="6">
         <v>50</v>
       </c>
-      <c r="J36" s="8">
+      <c r="J36" s="6">
         <v>20</v>
       </c>
-      <c r="K36" s="8">
+      <c r="K36" s="6">
         <v>45</v>
       </c>
-      <c r="L36" s="8">
-        <v>0</v>
-      </c>
-      <c r="M36" s="9" t="s">
+      <c r="L36" s="6">
+        <v>0</v>
+      </c>
+      <c r="M36" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="8">
+      <c r="A37" s="6">
         <v>5</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E37" s="8">
+      <c r="E37" s="6">
         <v>25</v>
       </c>
-      <c r="F37" s="8">
+      <c r="F37" s="6">
         <v>50</v>
       </c>
-      <c r="G37" s="8">
+      <c r="G37" s="6">
         <v>90</v>
       </c>
-      <c r="H37" s="8">
+      <c r="H37" s="6">
         <v>35</v>
       </c>
-      <c r="I37" s="8">
+      <c r="I37" s="6">
         <v>70</v>
       </c>
-      <c r="J37" s="8">
+      <c r="J37" s="6">
         <v>30</v>
       </c>
-      <c r="K37" s="8">
+      <c r="K37" s="6">
         <v>65</v>
       </c>
-      <c r="L37" s="8">
-        <v>0</v>
-      </c>
-      <c r="M37" s="9" t="s">
+      <c r="L37" s="6">
+        <v>0</v>
+      </c>
+      <c r="M37" s="7" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3688,207 +3694,207 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="8">
+      <c r="A39" s="6">
         <v>5</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D39" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E39" s="8">
+      <c r="E39" s="6">
         <v>20</v>
       </c>
-      <c r="F39" s="8">
+      <c r="F39" s="6">
         <v>45</v>
       </c>
-      <c r="G39" s="8">
+      <c r="G39" s="6">
         <v>90</v>
       </c>
-      <c r="H39" s="8">
+      <c r="H39" s="6">
         <v>30</v>
       </c>
-      <c r="I39" s="8">
+      <c r="I39" s="6">
         <v>70</v>
       </c>
-      <c r="J39" s="8">
+      <c r="J39" s="6">
         <v>25</v>
       </c>
-      <c r="K39" s="8">
+      <c r="K39" s="6">
         <v>60</v>
       </c>
-      <c r="L39" s="8">
-        <v>0</v>
-      </c>
-      <c r="M39" s="9" t="s">
+      <c r="L39" s="6">
+        <v>0</v>
+      </c>
+      <c r="M39" s="7" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="8">
+      <c r="A40" s="6">
         <v>5</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D40" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E40" s="8">
-        <v>0</v>
-      </c>
-      <c r="F40" s="8">
+      <c r="E40" s="6">
+        <v>0</v>
+      </c>
+      <c r="F40" s="6">
         <v>30</v>
       </c>
-      <c r="G40" s="8">
+      <c r="G40" s="6">
         <v>70</v>
       </c>
-      <c r="H40" s="8">
+      <c r="H40" s="6">
         <v>15</v>
       </c>
-      <c r="I40" s="8">
+      <c r="I40" s="6">
         <v>55</v>
       </c>
-      <c r="J40" s="8">
+      <c r="J40" s="6">
         <v>10</v>
       </c>
-      <c r="K40" s="8">
+      <c r="K40" s="6">
         <v>45</v>
       </c>
-      <c r="L40" s="8">
-        <v>0</v>
-      </c>
-      <c r="M40" s="9" t="s">
+      <c r="L40" s="6">
+        <v>0</v>
+      </c>
+      <c r="M40" s="7" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="8">
+      <c r="A41" s="6">
         <v>5</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D41" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E41" s="8">
+      <c r="E41" s="6">
         <v>5</v>
       </c>
-      <c r="F41" s="8">
+      <c r="F41" s="6">
         <v>10</v>
       </c>
-      <c r="G41" s="8">
+      <c r="G41" s="6">
         <v>15</v>
       </c>
-      <c r="H41" s="8">
+      <c r="H41" s="6">
         <v>8</v>
       </c>
-      <c r="I41" s="8">
+      <c r="I41" s="6">
         <v>15</v>
       </c>
-      <c r="J41" s="8">
+      <c r="J41" s="6">
         <v>5</v>
       </c>
-      <c r="K41" s="8">
+      <c r="K41" s="6">
         <v>10</v>
       </c>
-      <c r="L41" s="8">
-        <v>0</v>
-      </c>
-      <c r="M41" s="9" t="s">
+      <c r="L41" s="6">
+        <v>0</v>
+      </c>
+      <c r="M41" s="7" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="8">
+      <c r="A42" s="6">
         <v>5</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D42" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E42" s="8">
-        <v>0</v>
-      </c>
-      <c r="F42" s="8">
+      <c r="E42" s="6">
+        <v>0</v>
+      </c>
+      <c r="F42" s="6">
         <v>15</v>
       </c>
-      <c r="G42" s="8">
+      <c r="G42" s="6">
         <v>30</v>
       </c>
-      <c r="H42" s="8">
+      <c r="H42" s="6">
         <v>10</v>
       </c>
-      <c r="I42" s="8">
+      <c r="I42" s="6">
         <v>25</v>
       </c>
-      <c r="J42" s="8">
+      <c r="J42" s="6">
         <v>5</v>
       </c>
-      <c r="K42" s="8">
+      <c r="K42" s="6">
         <v>20</v>
       </c>
-      <c r="L42" s="8">
-        <v>0</v>
-      </c>
-      <c r="M42" s="9" t="s">
+      <c r="L42" s="6">
+        <v>0</v>
+      </c>
+      <c r="M42" s="7" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="8">
+      <c r="A43" s="6">
         <v>5</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E43" s="8">
+      <c r="E43" s="6">
         <v>20</v>
       </c>
-      <c r="F43" s="8">
+      <c r="F43" s="6">
         <v>38</v>
       </c>
-      <c r="G43" s="8">
+      <c r="G43" s="6">
         <v>70</v>
       </c>
-      <c r="H43" s="8">
+      <c r="H43" s="6">
         <v>20</v>
       </c>
-      <c r="I43" s="8">
+      <c r="I43" s="6">
         <v>45</v>
       </c>
-      <c r="J43" s="8">
+      <c r="J43" s="6">
         <v>15</v>
       </c>
-      <c r="K43" s="8">
+      <c r="K43" s="6">
         <v>40</v>
       </c>
-      <c r="L43" s="8">
-        <v>0</v>
-      </c>
-      <c r="M43" s="9" t="s">
+      <c r="L43" s="6">
+        <v>0</v>
+      </c>
+      <c r="M43" s="7" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3934,43 +3940,43 @@
       </c>
     </row>
     <row r="45" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="8">
+      <c r="A45" s="6">
         <v>5</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D45" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E45" s="8">
+      <c r="E45" s="6">
         <v>50</v>
       </c>
-      <c r="F45" s="8">
+      <c r="F45" s="6">
         <v>70</v>
       </c>
-      <c r="G45" s="8">
+      <c r="G45" s="6">
         <v>115</v>
       </c>
-      <c r="H45" s="8">
+      <c r="H45" s="6">
         <v>40</v>
       </c>
-      <c r="I45" s="8">
+      <c r="I45" s="6">
         <v>80</v>
       </c>
-      <c r="J45" s="8">
+      <c r="J45" s="6">
         <v>25</v>
       </c>
-      <c r="K45" s="8">
+      <c r="K45" s="6">
         <v>55</v>
       </c>
-      <c r="L45" s="8">
-        <v>0</v>
-      </c>
-      <c r="M45" s="9" t="s">
+      <c r="L45" s="6">
+        <v>0</v>
+      </c>
+      <c r="M45" s="7" t="s">
         <v>155</v>
       </c>
     </row>
@@ -4098,43 +4104,43 @@
       </c>
     </row>
     <row r="49" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="8">
+      <c r="A49" s="6">
         <v>5</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="C49" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="D49" s="8" t="s">
+      <c r="D49" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E49" s="8">
+      <c r="E49" s="6">
         <v>10</v>
       </c>
-      <c r="F49" s="8">
+      <c r="F49" s="6">
         <v>18</v>
       </c>
-      <c r="G49" s="8">
+      <c r="G49" s="6">
         <v>30</v>
       </c>
-      <c r="H49" s="8">
+      <c r="H49" s="6">
         <v>12</v>
       </c>
-      <c r="I49" s="8">
+      <c r="I49" s="6">
         <v>20</v>
       </c>
-      <c r="J49" s="8">
+      <c r="J49" s="6">
         <v>8</v>
       </c>
-      <c r="K49" s="8">
+      <c r="K49" s="6">
         <v>15</v>
       </c>
-      <c r="L49" s="8">
-        <v>0</v>
-      </c>
-      <c r="M49" s="9" t="s">
+      <c r="L49" s="6">
+        <v>0</v>
+      </c>
+      <c r="M49" s="7" t="s">
         <v>167</v>
       </c>
     </row>
@@ -4180,1099 +4186,1191 @@
       </c>
     </row>
     <row r="51" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="8">
+      <c r="A51" s="6">
         <v>5</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="C51" s="6" t="s">
         <v>172</v>
       </c>
       <c r="D51" t="s">
         <v>59</v>
       </c>
-      <c r="E51" s="8">
+      <c r="E51" s="6">
         <v>5</v>
       </c>
-      <c r="F51" s="8">
+      <c r="F51" s="6">
         <v>10</v>
       </c>
-      <c r="G51" s="8">
+      <c r="G51" s="6">
         <v>15</v>
       </c>
-      <c r="H51" s="8">
+      <c r="H51" s="6">
         <v>5</v>
       </c>
-      <c r="I51" s="8">
+      <c r="I51" s="6">
         <v>12</v>
       </c>
-      <c r="J51" s="8">
+      <c r="J51" s="6">
         <v>3</v>
       </c>
-      <c r="K51" s="8">
+      <c r="K51" s="6">
         <v>8</v>
       </c>
-      <c r="L51" s="8">
+      <c r="L51" s="6">
         <v>10</v>
       </c>
-      <c r="M51" s="9" t="s">
+      <c r="M51" s="7" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="8">
+      <c r="A52" s="6">
         <v>5</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="C52" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D52" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="E52" s="8">
+      <c r="E52" s="6">
         <v>600</v>
       </c>
-      <c r="F52" s="8">
+      <c r="F52" s="6">
         <v>800</v>
       </c>
-      <c r="G52" s="8">
+      <c r="G52" s="6">
         <v>1200</v>
       </c>
-      <c r="H52" s="8">
+      <c r="H52" s="6">
         <v>800</v>
       </c>
-      <c r="I52" s="8">
+      <c r="I52" s="6">
         <v>1200</v>
       </c>
-      <c r="J52" s="8">
+      <c r="J52" s="6">
         <v>800</v>
       </c>
-      <c r="K52" s="8">
+      <c r="K52" s="6">
         <v>1200</v>
       </c>
-      <c r="L52" s="8">
-        <v>0</v>
-      </c>
-      <c r="M52" s="9" t="s">
+      <c r="L52" s="6">
+        <v>0</v>
+      </c>
+      <c r="M52" s="7" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="8">
+      <c r="A53" s="6">
         <v>5</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="C53" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="D53" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="E53" s="8">
+      <c r="E53" s="6">
         <v>300</v>
       </c>
-      <c r="F53" s="8">
+      <c r="F53" s="6">
         <v>400</v>
       </c>
-      <c r="G53" s="8">
+      <c r="G53" s="6">
         <v>650</v>
       </c>
-      <c r="H53" s="8">
+      <c r="H53" s="6">
         <v>400</v>
       </c>
-      <c r="I53" s="8">
+      <c r="I53" s="6">
         <v>650</v>
       </c>
-      <c r="J53" s="8">
+      <c r="J53" s="6">
         <v>400</v>
       </c>
-      <c r="K53" s="8">
+      <c r="K53" s="6">
         <v>650</v>
       </c>
-      <c r="L53" s="8">
-        <v>0</v>
-      </c>
-      <c r="M53" s="10" t="s">
+      <c r="L53" s="6">
+        <v>0</v>
+      </c>
+      <c r="M53" s="8" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="8">
+      <c r="A54" s="6">
         <v>5</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C54" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="D54" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E54" s="8">
+      <c r="E54" s="6">
         <v>20</v>
       </c>
-      <c r="F54" s="8">
+      <c r="F54" s="6">
         <v>30</v>
       </c>
-      <c r="G54" s="8">
+      <c r="G54" s="6">
         <v>90</v>
       </c>
-      <c r="H54" s="8">
+      <c r="H54" s="6">
         <v>30</v>
       </c>
-      <c r="I54" s="8">
+      <c r="I54" s="6">
         <v>90</v>
       </c>
-      <c r="J54" s="8">
+      <c r="J54" s="6">
         <v>30</v>
       </c>
-      <c r="K54" s="8">
+      <c r="K54" s="6">
         <v>90</v>
       </c>
-      <c r="L54" s="8">
+      <c r="L54" s="6">
         <v>40</v>
       </c>
-      <c r="M54" s="10" t="s">
+      <c r="M54" s="8" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="8">
+      <c r="A55" s="6">
         <v>5</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C55" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="D55" s="8" t="s">
+      <c r="D55" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E55" s="8">
+      <c r="E55" s="6">
         <v>5</v>
       </c>
-      <c r="F55" s="8">
+      <c r="F55" s="6">
         <v>8</v>
       </c>
-      <c r="G55" s="8">
+      <c r="G55" s="6">
         <v>18</v>
       </c>
-      <c r="H55" s="8">
+      <c r="H55" s="6">
         <v>6</v>
       </c>
-      <c r="I55" s="8">
+      <c r="I55" s="6">
         <v>15</v>
       </c>
-      <c r="J55" s="8">
+      <c r="J55" s="6">
         <v>5</v>
       </c>
-      <c r="K55" s="8">
+      <c r="K55" s="6">
         <v>12</v>
       </c>
-      <c r="L55" s="8">
-        <v>0</v>
-      </c>
-      <c r="M55" s="10" t="s">
+      <c r="L55" s="6">
+        <v>0</v>
+      </c>
+      <c r="M55" s="8" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="44">
+      <c r="A56" s="49">
         <v>5</v>
       </c>
-      <c r="B56" s="45"/>
-      <c r="C56" s="45"/>
-      <c r="D56" s="45"/>
-      <c r="E56" s="45"/>
-      <c r="F56" s="45"/>
-      <c r="G56" s="45"/>
-      <c r="H56" s="45"/>
-      <c r="I56" s="45"/>
-      <c r="J56" s="45"/>
-      <c r="K56" s="45"/>
-      <c r="L56" s="45"/>
-      <c r="M56" s="46"/>
+      <c r="B56" s="49" t="s">
+        <v>479</v>
+      </c>
+      <c r="C56" s="49" t="s">
+        <v>478</v>
+      </c>
+      <c r="D56" s="49" t="s">
+        <v>94</v>
+      </c>
+      <c r="E56" s="49">
+        <v>0</v>
+      </c>
+      <c r="F56" s="49">
+        <v>1500</v>
+      </c>
+      <c r="G56" s="49">
+        <v>2500</v>
+      </c>
+      <c r="H56" s="49">
+        <v>1500</v>
+      </c>
+      <c r="I56" s="49">
+        <v>2500</v>
+      </c>
+      <c r="J56" s="49">
+        <v>1500</v>
+      </c>
+      <c r="K56" s="49">
+        <v>2500</v>
+      </c>
+      <c r="L56" s="49">
+        <v>2000</v>
+      </c>
+      <c r="M56" s="50" t="s">
+        <v>526</v>
+      </c>
     </row>
     <row r="57" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="8">
+      <c r="A57" s="6">
         <v>5</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="D57" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E57" s="8">
+      <c r="E57" s="6">
         <v>8</v>
       </c>
-      <c r="F57" s="8">
+      <c r="F57" s="6">
         <v>18</v>
       </c>
-      <c r="G57" s="8">
+      <c r="G57" s="6">
         <v>35</v>
       </c>
-      <c r="H57" s="8">
+      <c r="H57" s="6">
         <v>10</v>
       </c>
-      <c r="I57" s="8">
+      <c r="I57" s="6">
         <v>25</v>
       </c>
-      <c r="J57" s="8">
+      <c r="J57" s="6">
         <v>8</v>
       </c>
-      <c r="K57" s="8">
+      <c r="K57" s="6">
         <v>20</v>
       </c>
-      <c r="L57" s="8">
-        <v>0</v>
-      </c>
-      <c r="M57" s="9" t="s">
+      <c r="L57" s="6">
+        <v>0</v>
+      </c>
+      <c r="M57" s="7" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="8">
+      <c r="A58" s="6">
         <v>5</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="D58" s="8" t="s">
+      <c r="D58" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E58" s="8">
+      <c r="E58" s="6">
         <v>10</v>
       </c>
-      <c r="F58" s="8">
+      <c r="F58" s="6">
         <v>15</v>
       </c>
-      <c r="G58" s="8">
+      <c r="G58" s="6">
         <v>50</v>
       </c>
-      <c r="H58" s="8">
+      <c r="H58" s="6">
         <v>15</v>
       </c>
-      <c r="I58" s="8">
+      <c r="I58" s="6">
         <v>40</v>
       </c>
-      <c r="J58" s="8">
+      <c r="J58" s="6">
         <v>3</v>
       </c>
-      <c r="K58" s="8">
+      <c r="K58" s="6">
         <v>30</v>
       </c>
-      <c r="L58" s="8">
-        <v>0</v>
-      </c>
-      <c r="M58" s="9" t="s">
+      <c r="L58" s="6">
+        <v>0</v>
+      </c>
+      <c r="M58" s="7" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="44">
+      <c r="A59" s="51">
         <v>5</v>
       </c>
-      <c r="B59" s="45"/>
-      <c r="C59" s="45"/>
-      <c r="D59" s="45"/>
-      <c r="E59" s="45"/>
-      <c r="F59" s="45"/>
-      <c r="G59" s="45"/>
-      <c r="H59" s="45"/>
-      <c r="I59" s="45"/>
-      <c r="J59" s="45"/>
-      <c r="K59" s="45"/>
-      <c r="L59" s="45"/>
-      <c r="M59" s="46"/>
+      <c r="B59" s="51" t="s">
+        <v>500</v>
+      </c>
+      <c r="C59" s="51" t="s">
+        <v>527</v>
+      </c>
+      <c r="D59" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="E59" s="51">
+        <v>5</v>
+      </c>
+      <c r="F59" s="51">
+        <v>15</v>
+      </c>
+      <c r="G59" s="51">
+        <v>30</v>
+      </c>
+      <c r="H59" s="51">
+        <v>8</v>
+      </c>
+      <c r="I59" s="51">
+        <v>20</v>
+      </c>
+      <c r="J59" s="51">
+        <v>5</v>
+      </c>
+      <c r="K59" s="51">
+        <v>15</v>
+      </c>
+      <c r="L59" s="51">
+        <v>0</v>
+      </c>
+      <c r="M59" s="52" t="s">
+        <v>528</v>
+      </c>
     </row>
     <row r="60" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="8">
+      <c r="A60" s="6">
         <v>5</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D60" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E60" s="8">
+      <c r="E60" s="6">
         <v>25000</v>
       </c>
-      <c r="F60" s="8">
+      <c r="F60" s="6">
         <v>40000</v>
       </c>
-      <c r="G60" s="8">
+      <c r="G60" s="6">
         <v>60000</v>
       </c>
-      <c r="H60" s="8">
+      <c r="H60" s="6">
         <v>40000</v>
       </c>
-      <c r="I60" s="8">
+      <c r="I60" s="6">
         <v>60000</v>
       </c>
-      <c r="J60" s="8">
+      <c r="J60" s="6">
         <v>40000</v>
       </c>
-      <c r="K60" s="8">
+      <c r="K60" s="6">
         <v>60000</v>
       </c>
-      <c r="L60" s="8">
-        <v>0</v>
-      </c>
-      <c r="M60" s="9" t="s">
+      <c r="L60" s="6">
+        <v>0</v>
+      </c>
+      <c r="M60" s="7" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="8">
+      <c r="A61" s="6">
         <v>5</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="C61" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="D61" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E61" s="8">
+      <c r="E61" s="6">
         <v>8</v>
       </c>
-      <c r="F61" s="8">
+      <c r="F61" s="6">
         <v>18</v>
       </c>
-      <c r="G61" s="8">
+      <c r="G61" s="6">
         <v>30</v>
       </c>
-      <c r="H61" s="8">
+      <c r="H61" s="6">
         <v>8</v>
       </c>
-      <c r="I61" s="8">
+      <c r="I61" s="6">
         <v>18</v>
       </c>
-      <c r="J61" s="8">
+      <c r="J61" s="6">
         <v>6</v>
       </c>
-      <c r="K61" s="8">
+      <c r="K61" s="6">
         <v>15</v>
       </c>
-      <c r="L61" s="8">
-        <v>0</v>
-      </c>
-      <c r="M61" s="9" t="s">
+      <c r="L61" s="6">
+        <v>0</v>
+      </c>
+      <c r="M61" s="7" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="51" t="s">
+      <c r="A62" s="46" t="s">
         <v>200</v>
       </c>
-      <c r="B62" s="51"/>
-      <c r="C62" s="51"/>
-      <c r="D62" s="51"/>
-      <c r="E62" s="51"/>
-      <c r="F62" s="51"/>
-      <c r="G62" s="51"/>
-      <c r="H62" s="51"/>
-      <c r="I62" s="51"/>
-      <c r="J62" s="51"/>
-      <c r="K62" s="51"/>
-      <c r="L62" s="51"/>
-      <c r="M62" s="51"/>
+      <c r="B62" s="46"/>
+      <c r="C62" s="46"/>
+      <c r="D62" s="46"/>
+      <c r="E62" s="46"/>
+      <c r="F62" s="46"/>
+      <c r="G62" s="46"/>
+      <c r="H62" s="46"/>
+      <c r="I62" s="46"/>
+      <c r="J62" s="46"/>
+      <c r="K62" s="46"/>
+      <c r="L62" s="46"/>
+      <c r="M62" s="46"/>
     </row>
     <row r="63" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="8">
+      <c r="A63" s="6">
         <v>6</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="C63" s="8" t="s">
+      <c r="C63" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="D63" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E63" s="8">
-        <v>0</v>
-      </c>
-      <c r="F63" s="8">
-        <v>0</v>
-      </c>
-      <c r="G63" s="8">
+      <c r="E63" s="6">
+        <v>0</v>
+      </c>
+      <c r="F63" s="6">
+        <v>0</v>
+      </c>
+      <c r="G63" s="6">
         <v>200</v>
       </c>
-      <c r="H63" s="8">
-        <v>0</v>
-      </c>
-      <c r="I63" s="8">
+      <c r="H63" s="6">
+        <v>0</v>
+      </c>
+      <c r="I63" s="6">
         <v>150</v>
       </c>
-      <c r="J63" s="8">
-        <v>0</v>
-      </c>
-      <c r="K63" s="8">
+      <c r="J63" s="6">
+        <v>0</v>
+      </c>
+      <c r="K63" s="6">
         <v>100</v>
       </c>
-      <c r="L63" s="8">
-        <v>0</v>
-      </c>
-      <c r="M63" s="9" t="s">
+      <c r="L63" s="6">
+        <v>0</v>
+      </c>
+      <c r="M63" s="7" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="8">
+      <c r="A64" s="6">
         <v>6</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="C64" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="D64" s="8" t="s">
+      <c r="D64" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E64" s="8">
+      <c r="E64" s="6">
         <v>25</v>
       </c>
-      <c r="F64" s="8">
+      <c r="F64" s="6">
         <v>50</v>
       </c>
-      <c r="G64" s="8">
+      <c r="G64" s="6">
         <v>100</v>
       </c>
-      <c r="H64" s="8">
-        <v>0</v>
-      </c>
-      <c r="I64" s="8">
+      <c r="H64" s="6">
+        <v>0</v>
+      </c>
+      <c r="I64" s="6">
         <v>80</v>
       </c>
-      <c r="J64" s="8">
-        <v>0</v>
-      </c>
-      <c r="K64" s="8">
+      <c r="J64" s="6">
+        <v>0</v>
+      </c>
+      <c r="K64" s="6">
         <v>60</v>
       </c>
-      <c r="L64" s="8">
-        <v>0</v>
-      </c>
-      <c r="M64" s="9" t="s">
+      <c r="L64" s="6">
+        <v>0</v>
+      </c>
+      <c r="M64" s="7" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="49" t="s">
+      <c r="A65" s="44" t="s">
         <v>207</v>
       </c>
-      <c r="B65" s="48"/>
-      <c r="C65" s="48"/>
-      <c r="D65" s="48"/>
-      <c r="E65" s="48"/>
-      <c r="F65" s="48"/>
-      <c r="G65" s="48"/>
-      <c r="H65" s="48"/>
-      <c r="I65" s="48"/>
-      <c r="J65" s="48"/>
-      <c r="K65" s="48"/>
-      <c r="L65" s="48"/>
-      <c r="M65" s="48"/>
+      <c r="B65" s="43"/>
+      <c r="C65" s="43"/>
+      <c r="D65" s="43"/>
+      <c r="E65" s="43"/>
+      <c r="F65" s="43"/>
+      <c r="G65" s="43"/>
+      <c r="H65" s="43"/>
+      <c r="I65" s="43"/>
+      <c r="J65" s="43"/>
+      <c r="K65" s="43"/>
+      <c r="L65" s="43"/>
+      <c r="M65" s="43"/>
     </row>
     <row r="66" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="8">
+      <c r="A66" s="6">
         <v>7</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="C66" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="D66" s="8" t="s">
+      <c r="D66" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E66" s="8">
+      <c r="E66" s="6">
         <v>10</v>
       </c>
-      <c r="F66" s="8">
+      <c r="F66" s="6">
         <v>25</v>
       </c>
-      <c r="G66" s="8">
+      <c r="G66" s="6">
         <v>55</v>
       </c>
-      <c r="H66" s="8">
-        <v>0</v>
-      </c>
-      <c r="I66" s="8">
-        <v>0</v>
-      </c>
-      <c r="J66" s="8">
+      <c r="H66" s="6">
+        <v>0</v>
+      </c>
+      <c r="I66" s="6">
+        <v>0</v>
+      </c>
+      <c r="J66" s="6">
         <v>15</v>
       </c>
-      <c r="K66" s="8">
+      <c r="K66" s="6">
         <v>35</v>
       </c>
-      <c r="L66" s="8">
-        <v>0</v>
-      </c>
-      <c r="M66" s="9" t="s">
+      <c r="L66" s="6">
+        <v>0</v>
+      </c>
+      <c r="M66" s="7" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="8">
+      <c r="A67" s="6">
         <v>7</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="C67" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="D67" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E67" s="8">
+      <c r="E67" s="6">
         <v>10</v>
       </c>
-      <c r="F67" s="8">
+      <c r="F67" s="6">
         <v>20</v>
       </c>
-      <c r="G67" s="8">
+      <c r="G67" s="6">
         <v>45</v>
       </c>
-      <c r="H67" s="8">
-        <v>0</v>
-      </c>
-      <c r="I67" s="8">
-        <v>0</v>
-      </c>
-      <c r="J67" s="8">
+      <c r="H67" s="6">
+        <v>0</v>
+      </c>
+      <c r="I67" s="6">
+        <v>0</v>
+      </c>
+      <c r="J67" s="6">
         <v>12</v>
       </c>
-      <c r="K67" s="8">
+      <c r="K67" s="6">
         <v>28</v>
       </c>
-      <c r="L67" s="8">
-        <v>0</v>
-      </c>
-      <c r="M67" s="9" t="s">
+      <c r="L67" s="6">
+        <v>0</v>
+      </c>
+      <c r="M67" s="7" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="8">
+      <c r="A68" s="6">
         <v>7</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="C68" s="8" t="s">
+      <c r="C68" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="D68" s="8" t="s">
+      <c r="D68" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E68" s="8">
+      <c r="E68" s="6">
         <v>5</v>
       </c>
-      <c r="F68" s="8">
+      <c r="F68" s="6">
         <v>10</v>
       </c>
-      <c r="G68" s="8">
+      <c r="G68" s="6">
         <v>20</v>
       </c>
-      <c r="H68" s="8">
-        <v>0</v>
-      </c>
-      <c r="I68" s="8">
-        <v>0</v>
-      </c>
-      <c r="J68" s="8">
+      <c r="H68" s="6">
+        <v>0</v>
+      </c>
+      <c r="I68" s="6">
+        <v>0</v>
+      </c>
+      <c r="J68" s="6">
         <v>5</v>
       </c>
-      <c r="K68" s="8">
+      <c r="K68" s="6">
         <v>15</v>
       </c>
-      <c r="L68" s="8">
-        <v>0</v>
-      </c>
-      <c r="M68" s="9" t="s">
+      <c r="L68" s="6">
+        <v>0</v>
+      </c>
+      <c r="M68" s="7" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="8">
+      <c r="A69" s="6">
         <v>7</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B69" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="C69" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="D69" s="8" t="s">
+      <c r="D69" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E69" s="8">
-        <v>0</v>
-      </c>
-      <c r="F69" s="8">
+      <c r="E69" s="6">
+        <v>0</v>
+      </c>
+      <c r="F69" s="6">
         <v>30</v>
       </c>
-      <c r="G69" s="8">
+      <c r="G69" s="6">
         <v>80</v>
       </c>
-      <c r="H69" s="8">
-        <v>0</v>
-      </c>
-      <c r="I69" s="8">
-        <v>0</v>
-      </c>
-      <c r="J69" s="8">
+      <c r="H69" s="6">
+        <v>0</v>
+      </c>
+      <c r="I69" s="6">
+        <v>0</v>
+      </c>
+      <c r="J69" s="6">
         <v>20</v>
       </c>
-      <c r="K69" s="8">
+      <c r="K69" s="6">
         <v>55</v>
       </c>
-      <c r="L69" s="8">
-        <v>0</v>
-      </c>
-      <c r="M69" s="9" t="s">
+      <c r="L69" s="6">
+        <v>0</v>
+      </c>
+      <c r="M69" s="7" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="8">
+      <c r="A70" s="6">
         <v>7</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="C70" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="D70" s="8" t="s">
+      <c r="D70" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E70" s="8">
+      <c r="E70" s="6">
         <v>5</v>
       </c>
-      <c r="F70" s="8">
+      <c r="F70" s="6">
         <v>10</v>
       </c>
-      <c r="G70" s="8">
+      <c r="G70" s="6">
         <v>20</v>
       </c>
-      <c r="H70" s="8">
-        <v>0</v>
-      </c>
-      <c r="I70" s="8">
-        <v>0</v>
-      </c>
-      <c r="J70" s="8">
+      <c r="H70" s="6">
+        <v>0</v>
+      </c>
+      <c r="I70" s="6">
+        <v>0</v>
+      </c>
+      <c r="J70" s="6">
         <v>5</v>
       </c>
-      <c r="K70" s="8">
+      <c r="K70" s="6">
         <v>12</v>
       </c>
-      <c r="L70" s="8">
-        <v>0</v>
-      </c>
-      <c r="M70" s="9" t="s">
+      <c r="L70" s="6">
+        <v>0</v>
+      </c>
+      <c r="M70" s="7" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
+      <c r="A71" s="46" t="s">
         <v>223</v>
       </c>
+      <c r="B71" s="46"/>
+      <c r="C71" s="46"/>
+      <c r="D71" s="46"/>
+      <c r="E71" s="46"/>
+      <c r="F71" s="46"/>
+      <c r="G71" s="46"/>
+      <c r="H71" s="46"/>
+      <c r="I71" s="46"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="46"/>
+      <c r="L71" s="46"/>
+      <c r="M71" s="46"/>
     </row>
     <row r="72" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="8">
+      <c r="A72" s="6">
         <v>8</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="C72" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="D72" s="8" t="s">
+      <c r="D72" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E72" s="8">
+      <c r="E72" s="6">
         <v>3</v>
       </c>
-      <c r="F72" s="8">
+      <c r="F72" s="6">
         <v>8</v>
       </c>
-      <c r="G72" s="8">
+      <c r="G72" s="6">
         <v>15</v>
       </c>
-      <c r="H72" s="8">
+      <c r="H72" s="6">
         <v>8</v>
       </c>
-      <c r="I72" s="8">
+      <c r="I72" s="6">
         <v>18</v>
       </c>
-      <c r="J72" s="8">
+      <c r="J72" s="6">
         <v>5</v>
       </c>
-      <c r="K72" s="8">
+      <c r="K72" s="6">
         <v>12</v>
       </c>
-      <c r="L72" s="8">
+      <c r="L72" s="6">
         <v>10</v>
       </c>
-      <c r="M72" s="9" t="s">
+      <c r="M72" s="7" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="8">
+      <c r="A73" s="6">
         <v>8</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B73" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="C73" s="8" t="s">
+      <c r="C73" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="D73" s="8" t="s">
+      <c r="D73" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E73" s="8">
-        <v>0</v>
-      </c>
-      <c r="F73" s="8">
+      <c r="E73" s="6">
+        <v>0</v>
+      </c>
+      <c r="F73" s="6">
         <v>10</v>
       </c>
-      <c r="G73" s="8">
+      <c r="G73" s="6">
         <v>20</v>
       </c>
-      <c r="H73" s="8">
+      <c r="H73" s="6">
         <v>15</v>
       </c>
-      <c r="I73" s="8">
+      <c r="I73" s="6">
         <v>35</v>
       </c>
-      <c r="J73" s="8">
+      <c r="J73" s="6">
         <v>10</v>
       </c>
-      <c r="K73" s="8">
+      <c r="K73" s="6">
         <v>25</v>
       </c>
-      <c r="L73" s="8">
+      <c r="L73" s="6">
         <v>35</v>
       </c>
-      <c r="M73" s="9" t="s">
+      <c r="M73" s="7" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="8">
+      <c r="A74" s="6">
         <v>8</v>
       </c>
-      <c r="B74" s="8" t="s">
+      <c r="B74" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="C74" s="8" t="s">
+      <c r="C74" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="D74" s="8" t="s">
+      <c r="D74" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E74" s="8">
+      <c r="E74" s="6">
         <v>8</v>
       </c>
-      <c r="F74" s="8">
+      <c r="F74" s="6">
         <v>8</v>
       </c>
-      <c r="G74" s="8">
+      <c r="G74" s="6">
         <v>10</v>
       </c>
-      <c r="H74" s="8">
+      <c r="H74" s="6">
         <v>5</v>
       </c>
-      <c r="I74" s="8">
+      <c r="I74" s="6">
         <v>12</v>
       </c>
-      <c r="J74" s="8">
+      <c r="J74" s="6">
         <v>3</v>
       </c>
-      <c r="K74" s="8">
+      <c r="K74" s="6">
         <v>8</v>
       </c>
-      <c r="L74" s="8">
+      <c r="L74" s="6">
         <v>20</v>
       </c>
-      <c r="M74" s="9" t="s">
+      <c r="M74" s="7" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="8">
+      <c r="A75" s="6">
         <v>8</v>
       </c>
-      <c r="B75" s="8" t="s">
+      <c r="B75" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C75" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="D75" s="8" t="s">
+      <c r="D75" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E75" s="8">
+      <c r="E75" s="6">
         <v>3</v>
       </c>
-      <c r="F75" s="8">
+      <c r="F75" s="6">
         <v>8</v>
       </c>
-      <c r="G75" s="8">
+      <c r="G75" s="6">
         <v>15</v>
       </c>
-      <c r="H75" s="8">
+      <c r="H75" s="6">
         <v>10</v>
       </c>
-      <c r="I75" s="8">
+      <c r="I75" s="6">
         <v>20</v>
       </c>
-      <c r="J75" s="8">
+      <c r="J75" s="6">
         <v>5</v>
       </c>
-      <c r="K75" s="8">
+      <c r="K75" s="6">
         <v>15</v>
       </c>
-      <c r="L75" s="8">
+      <c r="L75" s="6">
         <v>25</v>
       </c>
-      <c r="M75" s="9" t="s">
+      <c r="M75" s="7" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="44">
+      <c r="A76" s="54">
         <v>8</v>
       </c>
-      <c r="B76" s="45"/>
-      <c r="C76" s="45"/>
-      <c r="D76" s="45"/>
-      <c r="E76" s="45"/>
-      <c r="F76" s="45"/>
-      <c r="G76" s="45"/>
-      <c r="H76" s="45"/>
-      <c r="I76" s="45"/>
-      <c r="J76" s="45"/>
-      <c r="K76" s="45"/>
-      <c r="L76" s="45"/>
-      <c r="M76" s="46"/>
+      <c r="B76" s="54" t="s">
+        <v>529</v>
+      </c>
+      <c r="C76" s="54" t="s">
+        <v>530</v>
+      </c>
+      <c r="D76" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="E76" s="54">
+        <v>3</v>
+      </c>
+      <c r="F76" s="54">
+        <v>6</v>
+      </c>
+      <c r="G76" s="54">
+        <v>12</v>
+      </c>
+      <c r="H76" s="54">
+        <v>8</v>
+      </c>
+      <c r="I76" s="54">
+        <v>15</v>
+      </c>
+      <c r="J76" s="54">
+        <v>5</v>
+      </c>
+      <c r="K76" s="54">
+        <v>10</v>
+      </c>
+      <c r="L76" s="54">
+        <v>15</v>
+      </c>
+      <c r="M76" s="55" t="s">
+        <v>531</v>
+      </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="8">
+      <c r="A77" s="6">
         <v>8</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B77" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="C77" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="D77" s="8" t="s">
+      <c r="D77" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E77" s="8">
+      <c r="E77" s="6">
         <v>8</v>
       </c>
-      <c r="F77" s="8">
+      <c r="F77" s="6">
         <v>10</v>
       </c>
-      <c r="G77" s="8">
+      <c r="G77" s="6">
         <v>20</v>
       </c>
-      <c r="H77" s="8">
+      <c r="H77" s="6">
         <v>10</v>
       </c>
-      <c r="I77" s="8">
+      <c r="I77" s="6">
         <v>20</v>
       </c>
-      <c r="J77" s="8">
+      <c r="J77" s="6">
         <v>5</v>
       </c>
-      <c r="K77" s="8">
+      <c r="K77" s="6">
         <v>15</v>
       </c>
-      <c r="L77" s="8">
+      <c r="L77" s="6">
         <v>20</v>
       </c>
-      <c r="M77" s="9" t="s">
+      <c r="M77" s="7" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A78" s="8">
+      <c r="A78" s="6">
         <v>8</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="B78" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="C78" s="8" t="s">
+      <c r="C78" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="D78" s="8" t="s">
+      <c r="D78" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E78" s="8">
+      <c r="E78" s="6">
         <v>30</v>
       </c>
-      <c r="F78" s="8">
+      <c r="F78" s="6">
         <v>75</v>
       </c>
-      <c r="G78" s="8">
+      <c r="G78" s="6">
         <v>150</v>
       </c>
-      <c r="H78" s="8">
+      <c r="H78" s="6">
         <v>75</v>
       </c>
-      <c r="I78" s="8">
+      <c r="I78" s="6">
         <v>150</v>
       </c>
-      <c r="J78" s="8">
+      <c r="J78" s="6">
         <v>75</v>
       </c>
-      <c r="K78" s="8">
+      <c r="K78" s="6">
         <v>150</v>
       </c>
-      <c r="L78" s="8">
+      <c r="L78" s="6">
         <v>30</v>
       </c>
-      <c r="M78" s="9" t="s">
+      <c r="M78" s="7" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A79" s="8">
+      <c r="A79" s="6">
         <v>8</v>
       </c>
-      <c r="B79" s="8" t="s">
+      <c r="B79" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="C79" s="8" t="s">
+      <c r="C79" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="D79" s="8" t="s">
+      <c r="D79" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E79" s="8">
-        <v>0</v>
-      </c>
-      <c r="F79" s="8">
+      <c r="E79" s="6">
+        <v>0</v>
+      </c>
+      <c r="F79" s="6">
         <v>3</v>
       </c>
-      <c r="G79" s="8">
+      <c r="G79" s="6">
         <v>8</v>
       </c>
-      <c r="H79" s="8">
+      <c r="H79" s="6">
         <v>3</v>
       </c>
-      <c r="I79" s="8">
+      <c r="I79" s="6">
         <v>10</v>
       </c>
-      <c r="J79" s="8">
+      <c r="J79" s="6">
         <v>2</v>
       </c>
-      <c r="K79" s="8">
+      <c r="K79" s="6">
         <v>8</v>
       </c>
-      <c r="L79" s="8">
+      <c r="L79" s="6">
         <v>12</v>
       </c>
-      <c r="M79" s="9" t="s">
+      <c r="M79" s="7" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A80" s="8">
+      <c r="A80" s="6">
         <v>8</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="B80" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="C80" s="8" t="s">
+      <c r="C80" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="D80" s="8" t="s">
+      <c r="D80" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E80" s="8">
+      <c r="E80" s="6">
         <v>75</v>
       </c>
-      <c r="F80" s="8">
+      <c r="F80" s="6">
         <v>150</v>
       </c>
-      <c r="G80" s="8">
+      <c r="G80" s="6">
         <v>250</v>
       </c>
-      <c r="H80" s="8">
+      <c r="H80" s="6">
         <v>150</v>
       </c>
-      <c r="I80" s="8">
+      <c r="I80" s="6">
         <v>250</v>
       </c>
-      <c r="J80" s="8">
+      <c r="J80" s="6">
         <v>150</v>
       </c>
-      <c r="K80" s="8">
+      <c r="K80" s="6">
         <v>250</v>
       </c>
-      <c r="L80" s="8">
+      <c r="L80" s="6">
         <v>10</v>
       </c>
-      <c r="M80" s="9" t="s">
+      <c r="M80" s="7" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="82" spans="1:1" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A82" s="5" t="s">
-        <v>248</v>
-      </c>
+    <row r="82" spans="1:13" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="53"/>
+      <c r="B82" s="53"/>
+      <c r="C82" s="53"/>
+      <c r="D82" s="53"/>
+      <c r="E82" s="53"/>
+      <c r="F82" s="53"/>
+      <c r="G82" s="53"/>
+      <c r="H82" s="53"/>
+      <c r="I82" s="53"/>
+      <c r="J82" s="53"/>
+      <c r="K82" s="53"/>
+      <c r="L82" s="53"/>
+      <c r="M82" s="53"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A76:M76"/>
+  <mergeCells count="11">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A5:M5"/>
     <mergeCell ref="A25:M25"/>
     <mergeCell ref="A35:M35"/>
-    <mergeCell ref="A56:M56"/>
     <mergeCell ref="A15:M15"/>
     <mergeCell ref="A29:M29"/>
     <mergeCell ref="A65:M65"/>
-    <mergeCell ref="A59:M59"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A10:M10"/>
     <mergeCell ref="A62:M62"/>
+    <mergeCell ref="A71:M71"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5293,940 +5391,940 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+    </row>
+    <row r="2" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="45" t="s">
         <v>249</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-    </row>
-    <row r="2" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+    </row>
+    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-    </row>
-    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="F4" s="6" t="s">
+    </row>
+    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="C5" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="D5" s="11">
+        <v>8</v>
+      </c>
+      <c r="E5" s="11">
+        <v>10</v>
+      </c>
+      <c r="F5" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="D5" s="13">
-        <v>8</v>
-      </c>
-      <c r="E5" s="13">
+    </row>
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="D6" s="11">
+        <v>1</v>
+      </c>
+      <c r="E6" s="11">
         <v>10</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F6" s="12" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="D7" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="11">
+        <v>10</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="C8" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="D8" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="11">
+        <v>10</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="D9" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="E9" s="11">
+        <v>10</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="D10" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="E10" s="11">
+        <v>10</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="D11" s="11">
+        <v>11</v>
+      </c>
+      <c r="E11" s="11"/>
+      <c r="F11" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="D12" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="E12" s="11"/>
+      <c r="F12" s="12" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="D13" s="11">
+        <v>8.5</v>
+      </c>
+      <c r="E13" s="11"/>
+      <c r="F13" s="12" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="D14" s="15">
+        <v>13.5</v>
+      </c>
+      <c r="E14" s="15"/>
+      <c r="F14" s="16" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="D15" s="15">
+        <v>11.5</v>
+      </c>
+      <c r="E15" s="15"/>
+      <c r="F15" s="16" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="D16" s="15">
+        <v>8.5</v>
+      </c>
+      <c r="E16" s="15"/>
+      <c r="F16" s="16" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="D17" s="15">
+        <v>6</v>
+      </c>
+      <c r="E17" s="15"/>
+      <c r="F17" s="16" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="D18" s="15">
+        <v>1.5</v>
+      </c>
+      <c r="E18" s="15"/>
+      <c r="F18" s="16" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="D19" s="15">
+        <v>1</v>
+      </c>
+      <c r="E19" s="15"/>
+      <c r="F19" s="16" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="D20" s="15">
+        <v>2</v>
+      </c>
+      <c r="E20" s="15"/>
+      <c r="F20" s="16" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="D21" s="15">
+        <v>3.5</v>
+      </c>
+      <c r="E21" s="15"/>
+      <c r="F21" s="16" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="D22" s="15">
+        <v>4</v>
+      </c>
+      <c r="E22" s="15"/>
+      <c r="F22" s="16" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="D23" s="15">
+        <v>4</v>
+      </c>
+      <c r="E23" s="15"/>
+      <c r="F23" s="16" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="D24" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="E24" s="15"/>
+      <c r="F24" s="16" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="D25" s="15">
+        <v>2</v>
+      </c>
+      <c r="E25" s="15"/>
+      <c r="F25" s="16" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="D26" s="15">
+        <v>3</v>
+      </c>
+      <c r="E26" s="15"/>
+      <c r="F26" s="16" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="D27" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="E27" s="15"/>
+      <c r="F27" s="16" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="D28" s="19">
+        <v>5</v>
+      </c>
+      <c r="E28" s="19">
+        <v>10</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="D29" s="19">
+        <v>2</v>
+      </c>
+      <c r="E29" s="19">
+        <v>10</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="D30" s="19">
+        <v>2</v>
+      </c>
+      <c r="E30" s="19">
+        <v>10</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="D31" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="E31" s="19">
+        <v>10</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="D32" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="E32" s="19">
+        <v>10</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="D33" s="19">
+        <v>1</v>
+      </c>
+      <c r="E33" s="19">
+        <v>10</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="D34" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="E34" s="19">
+        <v>10</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="D35" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="E35" s="19">
+        <v>10</v>
+      </c>
+      <c r="F35" s="20" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="D36" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="E36" s="19">
+        <v>10</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="D37" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="E37" s="19">
+        <v>10</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="D38" s="19">
+        <v>1</v>
+      </c>
+      <c r="E38" s="19">
+        <v>10</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="D39" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="E39" s="19">
+        <v>10</v>
+      </c>
+      <c r="F39" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="D6" s="13">
+    </row>
+    <row r="40" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="B40" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="C40" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="D40" s="23">
+        <v>5</v>
+      </c>
+      <c r="E40" s="23">
+        <v>5</v>
+      </c>
+      <c r="F40" s="24" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="B41" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="C41" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="D41" s="23">
+        <v>0</v>
+      </c>
+      <c r="E41" s="23">
+        <v>12</v>
+      </c>
+      <c r="F41" s="24" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="B42" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="C42" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="D42" s="23">
+        <v>2</v>
+      </c>
+      <c r="E42" s="23">
+        <v>12</v>
+      </c>
+      <c r="F42" s="24" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="C43" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="D43" s="23">
+        <v>4</v>
+      </c>
+      <c r="E43" s="23">
+        <v>12</v>
+      </c>
+      <c r="F43" s="24" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="B44" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="C44" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="D44" s="23">
+        <v>6</v>
+      </c>
+      <c r="E44" s="23">
+        <v>12</v>
+      </c>
+      <c r="F44" s="24" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="B45" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="C45" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="D45" s="23">
         <v>1</v>
       </c>
-      <c r="E6" s="13">
-        <v>10</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="D7" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="E7" s="13">
-        <v>10</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="D8" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="E8" s="13">
-        <v>10</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="D9" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="E9" s="13">
-        <v>10</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="D10" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="E10" s="13">
-        <v>10</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="D11" s="13">
-        <v>11</v>
-      </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="14" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="D12" s="13">
-        <v>9.5</v>
-      </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="14" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="D13" s="13">
-        <v>8.5</v>
-      </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="14" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="D14" s="17">
-        <v>13.5</v>
-      </c>
-      <c r="E14" s="17"/>
-      <c r="F14" s="18" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="D15" s="17">
-        <v>11.5</v>
-      </c>
-      <c r="E15" s="17"/>
-      <c r="F15" s="18" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="D16" s="17">
-        <v>8.5</v>
-      </c>
-      <c r="E16" s="17"/>
-      <c r="F16" s="18" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="D17" s="17">
-        <v>6</v>
-      </c>
-      <c r="E17" s="17"/>
-      <c r="F17" s="18" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="D18" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="E18" s="17"/>
-      <c r="F18" s="18" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="D19" s="17">
-        <v>1</v>
-      </c>
-      <c r="E19" s="17"/>
-      <c r="F19" s="18" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="D20" s="17">
+      <c r="E45" s="23">
+        <v>12</v>
+      </c>
+      <c r="F45" s="24" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="B46" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="C46" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="D46" s="23">
         <v>2</v>
       </c>
-      <c r="E20" s="17"/>
-      <c r="F20" s="18" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>283</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="D21" s="17">
-        <v>3.5</v>
-      </c>
-      <c r="E21" s="17"/>
-      <c r="F21" s="18" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>283</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="D22" s="17">
+      <c r="E46" s="23">
+        <v>12</v>
+      </c>
+      <c r="F46" s="24" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="B47" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="C47" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="D47" s="23">
+        <v>3</v>
+      </c>
+      <c r="E47" s="23">
+        <v>12</v>
+      </c>
+      <c r="F47" s="24" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="B48" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="C48" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="D48" s="23">
         <v>4</v>
       </c>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>283</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="D23" s="17">
-        <v>4</v>
-      </c>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>283</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="D24" s="17">
-        <v>2.5</v>
-      </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="18" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>283</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="D25" s="17">
-        <v>2</v>
-      </c>
-      <c r="E25" s="17"/>
-      <c r="F25" s="18" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>283</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="D26" s="17">
-        <v>3</v>
-      </c>
-      <c r="E26" s="17"/>
-      <c r="F26" s="18" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>283</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="D27" s="17">
-        <v>0.5</v>
-      </c>
-      <c r="E27" s="17"/>
-      <c r="F27" s="18" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="D28" s="21">
+      <c r="E48" s="23">
+        <v>12</v>
+      </c>
+      <c r="F48" s="24" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="B49" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="C49" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="D49" s="23">
         <v>5</v>
       </c>
-      <c r="E28" s="21">
-        <v>10</v>
-      </c>
-      <c r="F28" s="22" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="D29" s="21">
-        <v>2</v>
-      </c>
-      <c r="E29" s="21">
-        <v>10</v>
-      </c>
-      <c r="F29" s="22" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="D30" s="21">
-        <v>2</v>
-      </c>
-      <c r="E30" s="21">
-        <v>10</v>
-      </c>
-      <c r="F30" s="22" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="D31" s="21">
-        <v>1.5</v>
-      </c>
-      <c r="E31" s="21">
-        <v>10</v>
-      </c>
-      <c r="F31" s="22" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="D32" s="21">
-        <v>1.5</v>
-      </c>
-      <c r="E32" s="21">
-        <v>10</v>
-      </c>
-      <c r="F32" s="22" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="D33" s="21">
-        <v>1</v>
-      </c>
-      <c r="E33" s="21">
-        <v>10</v>
-      </c>
-      <c r="F33" s="22" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="D34" s="21">
-        <v>0.5</v>
-      </c>
-      <c r="E34" s="21">
-        <v>10</v>
-      </c>
-      <c r="F34" s="22" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="B35" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="D35" s="21">
-        <v>0.5</v>
-      </c>
-      <c r="E35" s="21">
-        <v>10</v>
-      </c>
-      <c r="F35" s="22" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="D36" s="21">
-        <v>0.5</v>
-      </c>
-      <c r="E36" s="21">
-        <v>10</v>
-      </c>
-      <c r="F36" s="22" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="D37" s="21">
-        <v>0.5</v>
-      </c>
-      <c r="E37" s="21">
-        <v>10</v>
-      </c>
-      <c r="F37" s="22" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="D38" s="21">
-        <v>1</v>
-      </c>
-      <c r="E38" s="21">
-        <v>10</v>
-      </c>
-      <c r="F38" s="22" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="B39" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="D39" s="21">
-        <v>0.5</v>
-      </c>
-      <c r="E39" s="21">
-        <v>10</v>
-      </c>
-      <c r="F39" s="22" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="23" t="s">
-        <v>304</v>
-      </c>
-      <c r="B40" s="24" t="s">
+      <c r="E49" s="23">
+        <v>12</v>
+      </c>
+      <c r="F49" s="24" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>321</v>
+      </c>
+      <c r="C50" s="26" t="s">
         <v>305</v>
       </c>
-      <c r="C40" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="D40" s="25">
-        <v>5</v>
-      </c>
-      <c r="E40" s="25">
-        <v>5</v>
-      </c>
-      <c r="F40" s="26" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="23" t="s">
-        <v>308</v>
-      </c>
-      <c r="B41" s="24" t="s">
-        <v>309</v>
-      </c>
-      <c r="C41" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="D41" s="25">
-        <v>0</v>
-      </c>
-      <c r="E41" s="25">
-        <v>12</v>
-      </c>
-      <c r="F41" s="26" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="23" t="s">
-        <v>308</v>
-      </c>
-      <c r="B42" s="24" t="s">
-        <v>309</v>
-      </c>
-      <c r="C42" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="D42" s="25">
-        <v>2</v>
-      </c>
-      <c r="E42" s="25">
-        <v>12</v>
-      </c>
-      <c r="F42" s="26" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="23" t="s">
-        <v>308</v>
-      </c>
-      <c r="B43" s="24" t="s">
-        <v>309</v>
-      </c>
-      <c r="C43" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="D43" s="25">
-        <v>4</v>
-      </c>
-      <c r="E43" s="25">
-        <v>12</v>
-      </c>
-      <c r="F43" s="26" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="23" t="s">
-        <v>308</v>
-      </c>
-      <c r="B44" s="24" t="s">
-        <v>309</v>
-      </c>
-      <c r="C44" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="D44" s="25">
-        <v>6</v>
-      </c>
-      <c r="E44" s="25">
-        <v>12</v>
-      </c>
-      <c r="F44" s="26" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="23" t="s">
-        <v>308</v>
-      </c>
-      <c r="B45" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="C45" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="D45" s="25">
-        <v>1</v>
-      </c>
-      <c r="E45" s="25">
-        <v>12</v>
-      </c>
-      <c r="F45" s="26" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="23" t="s">
-        <v>308</v>
-      </c>
-      <c r="B46" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="C46" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="D46" s="25">
-        <v>2</v>
-      </c>
-      <c r="E46" s="25">
-        <v>12</v>
-      </c>
-      <c r="F46" s="26" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="23" t="s">
-        <v>308</v>
-      </c>
-      <c r="B47" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="C47" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="D47" s="25">
-        <v>3</v>
-      </c>
-      <c r="E47" s="25">
-        <v>12</v>
-      </c>
-      <c r="F47" s="26" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="23" t="s">
-        <v>308</v>
-      </c>
-      <c r="B48" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="C48" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="D48" s="25">
-        <v>4</v>
-      </c>
-      <c r="E48" s="25">
-        <v>12</v>
-      </c>
-      <c r="F48" s="26" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="23" t="s">
-        <v>308</v>
-      </c>
-      <c r="B49" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="C49" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="D49" s="25">
-        <v>5</v>
-      </c>
-      <c r="E49" s="25">
-        <v>12</v>
-      </c>
-      <c r="F49" s="26" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="27" t="s">
-        <v>321</v>
-      </c>
-      <c r="B50" s="28" t="s">
+      <c r="D50" s="27">
+        <v>20</v>
+      </c>
+      <c r="E50" s="27">
+        <v>20</v>
+      </c>
+      <c r="F50" s="28" t="s">
         <v>322</v>
       </c>
-      <c r="C50" s="28" t="s">
-        <v>306</v>
-      </c>
-      <c r="D50" s="29">
-        <v>20</v>
-      </c>
-      <c r="E50" s="29">
-        <v>20</v>
-      </c>
-      <c r="F50" s="30" t="s">
+    </row>
+    <row r="52" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="45" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="50" t="s">
-        <v>324</v>
-      </c>
-      <c r="B52" s="48"/>
-      <c r="C52" s="48"/>
-      <c r="D52" s="48"/>
-      <c r="E52" s="48"/>
-      <c r="F52" s="48"/>
+      <c r="B52" s="43"/>
+      <c r="C52" s="43"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="43"/>
+      <c r="F52" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -6251,137 +6349,137 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="42" t="s">
+        <v>324</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+    </row>
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-    </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="D3" s="6" t="s">
+    </row>
+    <row r="4" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="29" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
+      <c r="B4" s="30" t="s">
         <v>330</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="C4" s="30" t="s">
         <v>331</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="D4" s="30" t="s">
         <v>332</v>
       </c>
-      <c r="D4" s="32" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="29" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="B5" s="30" t="s">
         <v>334</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="C5" s="30" t="s">
         <v>335</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="D5" s="30" t="s">
         <v>336</v>
       </c>
-      <c r="D5" s="32" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="s">
+      <c r="B6" s="30" t="s">
+        <v>334</v>
+      </c>
+      <c r="C6" s="30" t="s">
         <v>338</v>
       </c>
-      <c r="B6" s="32" t="s">
-        <v>335</v>
-      </c>
-      <c r="C6" s="32" t="s">
+      <c r="D6" s="30" t="s">
         <v>339</v>
       </c>
-      <c r="D6" s="32" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="29" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="31" t="s">
+      <c r="B7" s="30" t="s">
         <v>341</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="C7" s="30" t="s">
         <v>342</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="D7" s="30" t="s">
         <v>343</v>
       </c>
-      <c r="D7" s="32" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="B8" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="30" t="s">
         <v>345</v>
       </c>
-      <c r="B8" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="32" t="s">
+      <c r="D8" s="30" t="s">
         <v>346</v>
       </c>
-      <c r="D8" s="32" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="29" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
+      <c r="B9" s="30" t="s">
         <v>348</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="C9" s="30" t="s">
         <v>349</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="D9" s="30" t="s">
         <v>350</v>
       </c>
-      <c r="D9" s="32" t="s">
+    </row>
+    <row r="10" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="29" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="B10" s="30" t="s">
         <v>352</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="C10" s="30" t="s">
         <v>353</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="D10" s="30" t="s">
         <v>354</v>
       </c>
-      <c r="D10" s="32" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="29" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
+      <c r="B11" s="30" t="s">
         <v>356</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="C11" s="30" t="s">
         <v>357</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="D11" s="30" t="s">
         <v>358</v>
-      </c>
-      <c r="D11" s="32" t="s">
-        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -6404,181 +6502,181 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="42" t="s">
+        <v>359</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+    </row>
+    <row r="2" spans="1:5" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="45" t="s">
         <v>360</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-    </row>
-    <row r="2" spans="1:5" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
-        <v>361</v>
-      </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="31" t="s">
+        <v>361</v>
+      </c>
+      <c r="B4" s="31" t="s">
         <v>362</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="C4" s="31" t="s">
         <v>363</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="D4" s="31" t="s">
         <v>364</v>
       </c>
-      <c r="D4" s="33" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="29" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="B5" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="30" t="s">
         <v>366</v>
       </c>
-      <c r="B5" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="32" t="s">
+      <c r="D5" s="30" t="s">
         <v>367</v>
       </c>
-      <c r="D5" s="32" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="s">
+      <c r="B6" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="30" t="s">
         <v>369</v>
       </c>
-      <c r="B6" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="32" t="s">
+      <c r="D6" s="30" t="s">
         <v>370</v>
       </c>
-      <c r="D6" s="32" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="29" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="31" t="s">
+      <c r="B7" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="30" t="s">
         <v>372</v>
       </c>
-      <c r="B7" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="32" t="s">
+      <c r="D7" s="30" t="s">
         <v>373</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="42" t="s">
+      <c r="A9" s="40" t="s">
+        <v>374</v>
+      </c>
+      <c r="B9" s="40" t="s">
         <v>375</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="C9" s="40" t="s">
         <v>376</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="D9" s="40" t="s">
         <v>377</v>
       </c>
-      <c r="D9" s="42" t="s">
+      <c r="E9" s="41" t="s">
         <v>378</v>
-      </c>
-      <c r="E9" s="43" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>379</v>
+      </c>
+      <c r="B10" t="s">
         <v>380</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>381</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>382</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>383</v>
       </c>
-      <c r="E10" t="s">
+    </row>
+    <row r="11" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="29" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
+      <c r="B11" s="30" t="s">
         <v>385</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="C11" s="30" t="s">
+        <v>381</v>
+      </c>
+      <c r="D11" s="30" t="s">
         <v>386</v>
       </c>
-      <c r="C11" s="32" t="s">
-        <v>382</v>
-      </c>
-      <c r="D11" s="32" t="s">
+      <c r="E11" t="s">
         <v>387</v>
       </c>
-      <c r="E11" t="s">
+    </row>
+    <row r="12" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="29" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="31" t="s">
+      <c r="B12" s="30" t="s">
         <v>389</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="C12" s="30" t="s">
+        <v>381</v>
+      </c>
+      <c r="D12" s="30" t="s">
         <v>390</v>
       </c>
-      <c r="C12" s="32" t="s">
-        <v>382</v>
-      </c>
-      <c r="D12" s="32" t="s">
+      <c r="E12" t="s">
         <v>391</v>
       </c>
-      <c r="E12" t="s">
+    </row>
+    <row r="13" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="29" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="31" t="s">
+      <c r="B13" s="30" t="s">
         <v>393</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="C13" s="30" t="s">
         <v>394</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="D13" s="30" t="s">
         <v>395</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="E13" t="s">
         <v>396</v>
       </c>
-      <c r="E13" t="s">
+    </row>
+    <row r="14" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="47"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="48" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="52"/>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="53" t="s">
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+    </row>
+    <row r="16" spans="1:5" ht="132" x14ac:dyDescent="0.25">
+      <c r="A16" s="32" t="s">
         <v>398</v>
-      </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-    </row>
-    <row r="16" spans="1:5" ht="132" x14ac:dyDescent="0.25">
-      <c r="A16" s="34" t="s">
-        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -6604,243 +6702,243 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="42" t="s">
+        <v>399</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+    </row>
+    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-    </row>
-    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="E3" s="6" t="s">
+    </row>
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="33" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="35" t="s">
+      <c r="B4" s="34" t="s">
         <v>405</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="C4" s="35">
+        <v>1.2</v>
+      </c>
+      <c r="D4" s="35">
+        <v>1.3</v>
+      </c>
+      <c r="E4" s="35">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="33" t="s">
         <v>406</v>
       </c>
-      <c r="C4" s="37">
+      <c r="B5" s="34" t="s">
+        <v>407</v>
+      </c>
+      <c r="C5" s="35">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D5" s="35">
         <v>1.2</v>
       </c>
-      <c r="D4" s="37">
-        <v>1.3</v>
-      </c>
-      <c r="E4" s="37">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="35" t="s">
-        <v>407</v>
-      </c>
-      <c r="B5" s="36" t="s">
+      <c r="E5" s="35">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="33" t="s">
         <v>408</v>
       </c>
-      <c r="C5" s="37">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D5" s="37">
-        <v>1.2</v>
-      </c>
-      <c r="E5" s="37">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
+      <c r="B6" s="34" t="s">
         <v>409</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="C6" s="35">
+        <v>1.05</v>
+      </c>
+      <c r="D6" s="35">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="E6" s="35">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="33" t="s">
         <v>410</v>
       </c>
-      <c r="C6" s="37">
+      <c r="B7" s="34" t="s">
+        <v>411</v>
+      </c>
+      <c r="C7" s="35">
+        <v>1</v>
+      </c>
+      <c r="D7" s="35">
         <v>1.05</v>
       </c>
-      <c r="D6" s="37">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="E6" s="37">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="35" t="s">
-        <v>411</v>
-      </c>
-      <c r="B7" s="36" t="s">
+      <c r="E7" s="35">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
         <v>412</v>
       </c>
-      <c r="C7" s="37">
+      <c r="B8" s="36" t="s">
+        <v>413</v>
+      </c>
+      <c r="C8" s="37">
+        <v>0.92</v>
+      </c>
+      <c r="D8" s="37">
+        <v>0.97</v>
+      </c>
+      <c r="E8" s="37">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="33" t="s">
+        <v>414</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>415</v>
+      </c>
+      <c r="C9" s="35">
+        <v>0.91</v>
+      </c>
+      <c r="D9" s="35">
+        <v>0.96</v>
+      </c>
+      <c r="E9" s="35">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="33" t="s">
+        <v>416</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>417</v>
+      </c>
+      <c r="C10" s="35">
+        <v>0.88</v>
+      </c>
+      <c r="D10" s="35">
+        <v>0.93</v>
+      </c>
+      <c r="E10" s="35">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="33" t="s">
+        <v>418</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>419</v>
+      </c>
+      <c r="C11" s="35">
+        <v>0.9</v>
+      </c>
+      <c r="D11" s="35">
+        <v>0.95</v>
+      </c>
+      <c r="E11" s="35">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="33" t="s">
+        <v>420</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>421</v>
+      </c>
+      <c r="C12" s="35">
+        <v>0.87</v>
+      </c>
+      <c r="D12" s="35">
+        <v>0.92</v>
+      </c>
+      <c r="E12" s="35">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="33" t="s">
+        <v>422</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>423</v>
+      </c>
+      <c r="C13" s="35">
+        <v>0.87</v>
+      </c>
+      <c r="D13" s="35">
+        <v>0.93</v>
+      </c>
+      <c r="E13" s="35">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="33" t="s">
+        <v>424</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>425</v>
+      </c>
+      <c r="C14" s="35">
+        <v>0.93</v>
+      </c>
+      <c r="D14" s="35">
         <v>1</v>
       </c>
-      <c r="D7" s="37">
-        <v>1.05</v>
-      </c>
-      <c r="E7" s="37">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>413</v>
-      </c>
-      <c r="B8" s="38" t="s">
-        <v>414</v>
-      </c>
-      <c r="C8" s="39">
-        <v>0.92</v>
-      </c>
-      <c r="D8" s="39">
-        <v>0.97</v>
-      </c>
-      <c r="E8" s="39">
-        <v>0.94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="35" t="s">
-        <v>415</v>
-      </c>
-      <c r="B9" s="36" t="s">
-        <v>416</v>
-      </c>
-      <c r="C9" s="37">
-        <v>0.91</v>
-      </c>
-      <c r="D9" s="37">
-        <v>0.96</v>
-      </c>
-      <c r="E9" s="37">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="35" t="s">
-        <v>417</v>
-      </c>
-      <c r="B10" s="36" t="s">
-        <v>418</v>
-      </c>
-      <c r="C10" s="37">
+      <c r="E14" s="35">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="33" t="s">
+        <v>426</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>427</v>
+      </c>
+      <c r="C15" s="35">
+        <v>0.82</v>
+      </c>
+      <c r="D15" s="35">
         <v>0.88</v>
       </c>
-      <c r="D10" s="37">
-        <v>0.93</v>
-      </c>
-      <c r="E10" s="37">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="35" t="s">
-        <v>419</v>
-      </c>
-      <c r="B11" s="36" t="s">
-        <v>420</v>
-      </c>
-      <c r="C11" s="37">
-        <v>0.9</v>
-      </c>
-      <c r="D11" s="37">
-        <v>0.95</v>
-      </c>
-      <c r="E11" s="37">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="35" t="s">
-        <v>421</v>
-      </c>
-      <c r="B12" s="36" t="s">
-        <v>422</v>
-      </c>
-      <c r="C12" s="37">
-        <v>0.87</v>
-      </c>
-      <c r="D12" s="37">
-        <v>0.92</v>
-      </c>
-      <c r="E12" s="37">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="35" t="s">
-        <v>423</v>
-      </c>
-      <c r="B13" s="36" t="s">
-        <v>424</v>
-      </c>
-      <c r="C13" s="37">
-        <v>0.87</v>
-      </c>
-      <c r="D13" s="37">
-        <v>0.93</v>
-      </c>
-      <c r="E13" s="37">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="35" t="s">
-        <v>425</v>
-      </c>
-      <c r="B14" s="36" t="s">
-        <v>426</v>
-      </c>
-      <c r="C14" s="37">
-        <v>0.93</v>
-      </c>
-      <c r="D14" s="37">
-        <v>1</v>
-      </c>
-      <c r="E14" s="37">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="35" t="s">
-        <v>427</v>
-      </c>
-      <c r="B15" s="36" t="s">
+      <c r="E15" s="35">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="45" t="s">
         <v>428</v>
       </c>
-      <c r="C15" s="37">
-        <v>0.82</v>
-      </c>
-      <c r="D15" s="37">
-        <v>0.88</v>
-      </c>
-      <c r="E15" s="37">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="50" t="s">
-        <v>429</v>
-      </c>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6863,598 +6961,598 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="42" t="s">
+        <v>429</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+    </row>
+    <row r="2" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="45" t="s">
         <v>430</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-    </row>
-    <row r="2" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="5" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="29" t="s">
         <v>433</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="B5" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="30" t="s">
         <v>434</v>
       </c>
-      <c r="B5" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="32" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="s">
+      <c r="B6" s="30" t="s">
         <v>436</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="C6" s="30" t="s">
         <v>437</v>
       </c>
-      <c r="C6" s="32" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="29" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="31" t="s">
+      <c r="B7" s="30" t="s">
         <v>439</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="C7" s="30" t="s">
         <v>440</v>
       </c>
-      <c r="C7" s="32" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="30" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="32" t="s">
+      <c r="C8" s="30" t="s">
         <v>442</v>
       </c>
-      <c r="C8" s="32" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="29" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
+      <c r="B9" s="30" t="s">
         <v>444</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="C9" s="30" t="s">
         <v>445</v>
       </c>
-      <c r="C9" s="32" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="29" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="B10" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="30"/>
+    </row>
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="29" t="s">
         <v>447</v>
       </c>
-      <c r="B10" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="32"/>
-    </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
+      <c r="B11" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="30"/>
+    </row>
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="29" t="s">
         <v>448</v>
       </c>
-      <c r="B11" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" s="32"/>
-    </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="31" t="s">
+      <c r="B12" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="30"/>
+    </row>
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="29" t="s">
         <v>449</v>
       </c>
-      <c r="B12" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" s="32"/>
-    </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="31" t="s">
+      <c r="B13" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="38" t="s">
         <v>450</v>
       </c>
-      <c r="B13" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="40" t="s">
+    </row>
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="29" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="31" t="s">
+      <c r="B14" s="30" t="s">
         <v>452</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="C14" s="30" t="s">
         <v>453</v>
       </c>
-      <c r="C14" s="32" t="s">
+    </row>
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="29" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
+      <c r="B15" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="C15" s="30"/>
+    </row>
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="29" t="s">
         <v>455</v>
       </c>
-      <c r="B15" s="32" t="s">
-        <v>230</v>
-      </c>
-      <c r="C15" s="32"/>
-    </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="31" t="s">
+      <c r="B16" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="C16" s="30"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="29" t="s">
         <v>456</v>
       </c>
-      <c r="B16" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="C16" s="32"/>
-    </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="31" t="s">
+      <c r="B17" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="C17" s="30"/>
+    </row>
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="29" t="s">
         <v>457</v>
       </c>
-      <c r="B17" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="C17" s="32"/>
-    </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="31" t="s">
+      <c r="B18" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="C18" s="30"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="29" t="s">
         <v>458</v>
       </c>
-      <c r="B18" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="C18" s="32"/>
-    </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
+      <c r="B19" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="C19" s="30" t="s">
         <v>459</v>
       </c>
-      <c r="B19" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="C19" s="32" t="s">
+    </row>
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="29" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="31" t="s">
+      <c r="B20" s="30" t="s">
         <v>461</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="C20" s="30"/>
+    </row>
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="29" t="s">
         <v>462</v>
       </c>
-      <c r="C20" s="32"/>
-    </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="31" t="s">
+      <c r="B21" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" s="30"/>
+    </row>
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="C22" s="30"/>
+    </row>
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="29" t="s">
         <v>463</v>
       </c>
-      <c r="B21" s="32" t="s">
-        <v>144</v>
-      </c>
-      <c r="C21" s="32"/>
-    </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="B22" s="32" t="s">
-        <v>141</v>
-      </c>
-      <c r="C22" s="32"/>
-    </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="31" t="s">
+      <c r="B23" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="C23" s="30"/>
+    </row>
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="29" t="s">
         <v>464</v>
       </c>
-      <c r="B23" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="C23" s="32"/>
-    </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="31" t="s">
+      <c r="B24" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="C24" s="30"/>
+    </row>
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="29" t="s">
         <v>465</v>
       </c>
-      <c r="B24" s="32" t="s">
+      <c r="B25" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="C24" s="32"/>
-    </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="31" t="s">
+      <c r="C25" s="30"/>
+    </row>
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="29" t="s">
         <v>466</v>
       </c>
-      <c r="B25" s="32" t="s">
-        <v>153</v>
-      </c>
-      <c r="C25" s="32"/>
-    </row>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="31" t="s">
+      <c r="B26" s="30" t="s">
         <v>467</v>
       </c>
-      <c r="B26" s="32" t="s">
+      <c r="C26" s="30" t="s">
         <v>468</v>
       </c>
-      <c r="C26" s="32" t="s">
+    </row>
+    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="29" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="31" t="s">
+      <c r="B27" s="30" t="s">
         <v>470</v>
       </c>
-      <c r="B27" s="32" t="s">
+      <c r="C27" s="30"/>
+    </row>
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="29" t="s">
         <v>471</v>
       </c>
-      <c r="C27" s="32"/>
-    </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="31" t="s">
+      <c r="B28" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="C28" s="30" t="s">
         <v>472</v>
       </c>
-      <c r="B28" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="C28" s="32" t="s">
+    </row>
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="29" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="31" t="s">
+      <c r="B29" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="C29" s="38" t="s">
         <v>474</v>
       </c>
-      <c r="B29" s="32" t="s">
-        <v>178</v>
-      </c>
-      <c r="C29" s="40" t="s">
+    </row>
+    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="29" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="31" t="s">
+      <c r="B30" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="C30" s="38" t="s">
         <v>476</v>
       </c>
-      <c r="B30" s="32" t="s">
-        <v>182</v>
-      </c>
-      <c r="C30" s="40" t="s">
+    </row>
+    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="29" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="31" t="s">
+      <c r="B31" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="C31" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="29" t="s">
         <v>478</v>
       </c>
-      <c r="B31" s="32" t="s">
-        <v>185</v>
-      </c>
-      <c r="C31" s="40" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="31" t="s">
+      <c r="B32" s="30" t="s">
         <v>479</v>
       </c>
-      <c r="B32" s="32" t="s">
+      <c r="C32" s="30" t="s">
         <v>480</v>
       </c>
-      <c r="C32" s="32" t="s">
+    </row>
+    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="29" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="31" t="s">
+      <c r="B33" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="30"/>
+    </row>
+    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="29" t="s">
         <v>482</v>
       </c>
-      <c r="B33" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" s="32"/>
-    </row>
-    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="31" t="s">
+      <c r="B34" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="C34" s="30" t="s">
         <v>483</v>
       </c>
-      <c r="B34" s="32" t="s">
-        <v>106</v>
-      </c>
-      <c r="C34" s="32" t="s">
+    </row>
+    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="29" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="31" t="s">
+      <c r="B35" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" s="30" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="29" t="s">
         <v>485</v>
       </c>
-      <c r="B35" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="C35" s="32" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="31" t="s">
+      <c r="B36" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C36" s="30"/>
+    </row>
+    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="29" t="s">
         <v>486</v>
       </c>
-      <c r="B36" s="32" t="s">
-        <v>92</v>
-      </c>
-      <c r="C36" s="32"/>
-    </row>
-    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="31" t="s">
+      <c r="B37" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" s="30" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="29" t="s">
         <v>487</v>
       </c>
-      <c r="B37" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="C37" s="32" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="31" t="s">
+      <c r="B38" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="C38" s="30"/>
+    </row>
+    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="29" t="s">
         <v>488</v>
       </c>
-      <c r="B38" s="32" t="s">
-        <v>110</v>
-      </c>
-      <c r="C38" s="32"/>
-    </row>
-    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="31" t="s">
+      <c r="B39" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="C39" s="30"/>
+    </row>
+    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="29" t="s">
         <v>489</v>
       </c>
-      <c r="B39" s="32" t="s">
-        <v>116</v>
-      </c>
-      <c r="C39" s="32"/>
-    </row>
-    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="31" t="s">
+      <c r="B40" s="30" t="s">
         <v>490</v>
       </c>
-      <c r="B40" s="32" t="s">
+      <c r="C40" s="30"/>
+    </row>
+    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="29" t="s">
         <v>491</v>
       </c>
-      <c r="C40" s="32"/>
-    </row>
-    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="31" t="s">
+      <c r="B41" s="30" t="s">
         <v>492</v>
       </c>
-      <c r="B41" s="32" t="s">
+      <c r="C41" s="30" t="s">
         <v>493</v>
       </c>
-      <c r="C41" s="32" t="s">
+    </row>
+    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="29" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="31" t="s">
+      <c r="B42" s="30" t="s">
+        <v>492</v>
+      </c>
+      <c r="C42" s="30" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="29" t="s">
         <v>495</v>
       </c>
-      <c r="B42" s="32" t="s">
+      <c r="B43" s="30" t="s">
+        <v>496</v>
+      </c>
+      <c r="C43" s="30" t="s">
         <v>493</v>
       </c>
-      <c r="C42" s="32" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="31" t="s">
-        <v>496</v>
-      </c>
-      <c r="B43" s="32" t="s">
+    </row>
+    <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="29" t="s">
         <v>497</v>
       </c>
-      <c r="C43" s="32" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="31" t="s">
+      <c r="B44" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="30"/>
+    </row>
+    <row r="45" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="B45" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="C45" s="30" t="s">
         <v>498</v>
       </c>
-      <c r="B44" s="32" t="s">
-        <v>188</v>
-      </c>
-      <c r="C44" s="32"/>
-    </row>
-    <row r="45" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="31" t="s">
-        <v>192</v>
-      </c>
-      <c r="B45" s="32" t="s">
-        <v>191</v>
-      </c>
-      <c r="C45" s="32" t="s">
+    </row>
+    <row r="46" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="29" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="31" t="s">
+      <c r="B46" s="30" t="s">
         <v>500</v>
       </c>
-      <c r="B46" s="32" t="s">
+      <c r="C46" s="30"/>
+    </row>
+    <row r="47" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="29" t="s">
         <v>501</v>
       </c>
-      <c r="C46" s="32"/>
-    </row>
-    <row r="47" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="31" t="s">
+      <c r="B47" s="30" t="s">
+        <v>500</v>
+      </c>
+      <c r="C47" s="30"/>
+    </row>
+    <row r="48" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="29" t="s">
         <v>502</v>
       </c>
-      <c r="B47" s="32" t="s">
-        <v>501</v>
-      </c>
-      <c r="C47" s="32"/>
-    </row>
-    <row r="48" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="31" t="s">
+      <c r="B48" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="C48" s="30" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="29" t="s">
         <v>503</v>
       </c>
-      <c r="B48" s="32" t="s">
-        <v>194</v>
-      </c>
-      <c r="C48" s="32" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="31" t="s">
+      <c r="B49" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="C49" s="30" t="s">
         <v>504</v>
       </c>
-      <c r="B49" s="32" t="s">
-        <v>113</v>
-      </c>
-      <c r="C49" s="32" t="s">
+    </row>
+    <row r="50" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="29" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="31" t="s">
+      <c r="B50" s="30" t="s">
         <v>506</v>
       </c>
-      <c r="B50" s="32" t="s">
+      <c r="C50" s="30"/>
+    </row>
+    <row r="51" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="29" t="s">
         <v>507</v>
       </c>
-      <c r="C50" s="32"/>
-    </row>
-    <row r="51" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="31" t="s">
+      <c r="B51" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="C51" s="38" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="29" t="s">
         <v>508</v>
       </c>
-      <c r="B51" s="32" t="s">
-        <v>122</v>
-      </c>
-      <c r="C51" s="40" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="31" t="s">
+      <c r="B52" s="30" t="s">
         <v>509</v>
       </c>
-      <c r="B52" s="32" t="s">
+      <c r="C52" s="39" t="s">
         <v>510</v>
       </c>
-      <c r="C52" s="41" t="s">
+    </row>
+    <row r="53" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="29" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="31" t="s">
+      <c r="B53" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="C53" s="39" t="s">
         <v>512</v>
-      </c>
-      <c r="B53" s="32" t="s">
-        <v>197</v>
-      </c>
-      <c r="C53" s="41" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B54" t="s">
         <v>132</v>
       </c>
       <c r="C54" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B55" t="s">
         <v>150</v>
       </c>
       <c r="C55" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B56" t="s">
         <v>156</v>
       </c>
       <c r="C56" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B57" t="s">
         <v>159</v>
       </c>
       <c r="C57" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B58" t="s">
         <v>162</v>
       </c>
       <c r="C58" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B59" t="s">
         <v>165</v>
       </c>
       <c r="C59" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B60" t="s">
         <v>168</v>
       </c>
       <c r="C60" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
